--- a/Project-QM/data_W12.xlsx
+++ b/Project-QM/data_W12.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jtinoco2\Downloads\Failures-PMI\Project-QM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Downloads\Failures-PMI\Project-QM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F485F5DD-93AF-4F22-B616-611699809FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9925FC19-D0A6-41D2-A1F2-F37F6884E26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1236" yWindow="420" windowWidth="20784" windowHeight="12240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="W12" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3483" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3485" uniqueCount="106">
   <si>
     <t>Role</t>
   </si>
@@ -336,6 +336,12 @@
   <si>
     <t>Hernandez Mayra</t>
   </si>
+  <si>
+    <t>504 =100</t>
+  </si>
+  <si>
+    <t>365 = 0%</t>
+  </si>
 </sst>
 </file>
 
@@ -437,7 +443,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -753,11 +759,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:G870"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:J870"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -780,7 +785,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="2" spans="1:10" s="8" customFormat="1">
       <c r="A2" s="6" t="s">
         <v>5</v>
       </c>
@@ -803,7 +808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" hidden="1">
+    <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
@@ -825,8 +830,11 @@
       <c r="G3" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" hidden="1">
+      <c r="J3">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="3" t="s">
         <v>5</v>
       </c>
@@ -848,8 +856,11 @@
       <c r="G4" s="5">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" hidden="1">
+      <c r="J4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
@@ -871,8 +882,11 @@
       <c r="G5" s="5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" hidden="1">
+      <c r="J5" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -895,7 +909,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:7" hidden="1">
+    <row r="7" spans="1:10">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
@@ -918,7 +932,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:7" hidden="1">
+    <row r="8" spans="1:10">
       <c r="A8" s="3" t="s">
         <v>5</v>
       </c>
@@ -941,7 +955,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
@@ -964,7 +978,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:7" hidden="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
         <v>5</v>
       </c>
@@ -987,7 +1001,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:7" hidden="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="3" t="s">
         <v>5</v>
       </c>
@@ -1010,7 +1024,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" hidden="1">
+    <row r="12" spans="1:10">
       <c r="A12" s="3" t="s">
         <v>5</v>
       </c>
@@ -1033,7 +1047,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:7" hidden="1">
+    <row r="13" spans="1:10">
       <c r="A13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1056,7 +1070,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:7" hidden="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1079,7 +1093,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:7" hidden="1">
+    <row r="15" spans="1:10">
       <c r="A15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1102,7 +1116,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:7" hidden="1">
+    <row r="16" spans="1:10">
       <c r="A16" s="3" t="s">
         <v>5</v>
       </c>
@@ -1125,7 +1139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" hidden="1">
+    <row r="17" spans="1:7">
       <c r="A17" s="3" t="s">
         <v>5</v>
       </c>
@@ -1148,7 +1162,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" hidden="1">
+    <row r="18" spans="1:7">
       <c r="A18" s="3" t="s">
         <v>5</v>
       </c>
@@ -1171,7 +1185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:7" hidden="1">
+    <row r="19" spans="1:7">
       <c r="A19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1194,7 +1208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" hidden="1">
+    <row r="20" spans="1:7">
       <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
@@ -1217,7 +1231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:7" hidden="1">
+    <row r="21" spans="1:7">
       <c r="A21" s="3" t="s">
         <v>5</v>
       </c>
@@ -1240,7 +1254,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:7" hidden="1">
+    <row r="22" spans="1:7">
       <c r="A22" s="3" t="s">
         <v>5</v>
       </c>
@@ -1263,7 +1277,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1">
+    <row r="23" spans="1:7">
       <c r="A23" s="3" t="s">
         <v>5</v>
       </c>
@@ -1286,7 +1300,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1">
+    <row r="24" spans="1:7">
       <c r="A24" s="3" t="s">
         <v>5</v>
       </c>
@@ -1309,7 +1323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1">
+    <row r="25" spans="1:7">
       <c r="A25" s="3" t="s">
         <v>5</v>
       </c>
@@ -1332,7 +1346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1">
+    <row r="26" spans="1:7">
       <c r="A26" s="3" t="s">
         <v>5</v>
       </c>
@@ -1355,7 +1369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:7" hidden="1">
+    <row r="27" spans="1:7">
       <c r="A27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1378,7 +1392,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:7" hidden="1">
+    <row r="28" spans="1:7">
       <c r="A28" s="3" t="s">
         <v>5</v>
       </c>
@@ -1401,7 +1415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:7" hidden="1">
+    <row r="29" spans="1:7">
       <c r="A29" s="3" t="s">
         <v>5</v>
       </c>
@@ -1424,7 +1438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:7" hidden="1">
+    <row r="30" spans="1:7">
       <c r="A30" s="3" t="s">
         <v>5</v>
       </c>
@@ -1447,7 +1461,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:7" hidden="1">
+    <row r="31" spans="1:7">
       <c r="A31" s="3" t="s">
         <v>5</v>
       </c>
@@ -1470,7 +1484,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:7" hidden="1">
+    <row r="32" spans="1:7">
       <c r="A32" s="3" t="s">
         <v>5</v>
       </c>
@@ -1493,7 +1507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:7" hidden="1">
+    <row r="33" spans="1:7">
       <c r="A33" s="3" t="s">
         <v>5</v>
       </c>
@@ -1516,7 +1530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" hidden="1">
+    <row r="34" spans="1:7">
       <c r="A34" s="3" t="s">
         <v>5</v>
       </c>
@@ -1539,7 +1553,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:7" hidden="1">
+    <row r="35" spans="1:7">
       <c r="A35" s="3" t="s">
         <v>5</v>
       </c>
@@ -1562,7 +1576,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:7" hidden="1">
+    <row r="36" spans="1:7">
       <c r="A36" s="3" t="s">
         <v>5</v>
       </c>
@@ -1585,7 +1599,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="37" spans="1:7" hidden="1">
+    <row r="37" spans="1:7">
       <c r="A37" s="3" t="s">
         <v>5</v>
       </c>
@@ -1608,7 +1622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:7" hidden="1">
+    <row r="38" spans="1:7">
       <c r="A38" s="3" t="s">
         <v>5</v>
       </c>
@@ -1631,7 +1645,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" hidden="1">
+    <row r="39" spans="1:7">
       <c r="A39" s="3" t="s">
         <v>5</v>
       </c>
@@ -1654,7 +1668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:7" hidden="1">
+    <row r="40" spans="1:7">
       <c r="A40" s="3" t="s">
         <v>5</v>
       </c>
@@ -1677,7 +1691,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" hidden="1">
+    <row r="41" spans="1:7">
       <c r="A41" s="3" t="s">
         <v>5</v>
       </c>
@@ -1700,7 +1714,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" hidden="1">
+    <row r="42" spans="1:7">
       <c r="A42" s="3" t="s">
         <v>5</v>
       </c>
@@ -1723,7 +1737,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="43" spans="1:7" hidden="1">
+    <row r="43" spans="1:7">
       <c r="A43" s="3" t="s">
         <v>5</v>
       </c>
@@ -1746,7 +1760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" hidden="1">
+    <row r="44" spans="1:7">
       <c r="A44" s="3" t="s">
         <v>5</v>
       </c>
@@ -1769,7 +1783,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="45" spans="1:7" s="8" customFormat="1">
       <c r="A45" s="6" t="s">
         <v>51</v>
       </c>
@@ -1792,7 +1806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" hidden="1">
+    <row r="46" spans="1:7">
       <c r="A46" s="3" t="s">
         <v>51</v>
       </c>
@@ -1815,7 +1829,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:7" hidden="1">
+    <row r="47" spans="1:7">
       <c r="A47" s="3" t="s">
         <v>51</v>
       </c>
@@ -1838,7 +1852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" hidden="1">
+    <row r="48" spans="1:7">
       <c r="A48" s="3" t="s">
         <v>51</v>
       </c>
@@ -1861,7 +1875,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:7" hidden="1">
+    <row r="49" spans="1:7">
       <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
@@ -1884,7 +1898,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:7" hidden="1">
+    <row r="50" spans="1:7">
       <c r="A50" s="3" t="s">
         <v>51</v>
       </c>
@@ -1907,7 +1921,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:7" hidden="1">
+    <row r="51" spans="1:7">
       <c r="A51" s="3" t="s">
         <v>51</v>
       </c>
@@ -1930,7 +1944,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="52" spans="1:7" hidden="1">
+    <row r="52" spans="1:7">
       <c r="A52" s="3" t="s">
         <v>51</v>
       </c>
@@ -1953,7 +1967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:7" hidden="1">
+    <row r="53" spans="1:7">
       <c r="A53" s="3" t="s">
         <v>51</v>
       </c>
@@ -1976,7 +1990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:7" hidden="1">
+    <row r="54" spans="1:7">
       <c r="A54" s="3" t="s">
         <v>51</v>
       </c>
@@ -1999,7 +2013,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:7" hidden="1">
+    <row r="55" spans="1:7">
       <c r="A55" s="3" t="s">
         <v>51</v>
       </c>
@@ -2022,7 +2036,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:7" hidden="1">
+    <row r="56" spans="1:7">
       <c r="A56" s="3" t="s">
         <v>51</v>
       </c>
@@ -2045,7 +2059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" hidden="1">
+    <row r="57" spans="1:7">
       <c r="A57" s="3" t="s">
         <v>51</v>
       </c>
@@ -2068,7 +2082,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="58" spans="1:7" hidden="1">
+    <row r="58" spans="1:7">
       <c r="A58" s="3" t="s">
         <v>51</v>
       </c>
@@ -2091,7 +2105,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:7" hidden="1">
+    <row r="59" spans="1:7">
       <c r="A59" s="3" t="s">
         <v>51</v>
       </c>
@@ -2114,7 +2128,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:7" hidden="1">
+    <row r="60" spans="1:7">
       <c r="A60" s="3" t="s">
         <v>51</v>
       </c>
@@ -2137,7 +2151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:7" hidden="1">
+    <row r="61" spans="1:7">
       <c r="A61" s="3" t="s">
         <v>51</v>
       </c>
@@ -2160,7 +2174,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" hidden="1">
+    <row r="62" spans="1:7">
       <c r="A62" s="3" t="s">
         <v>51</v>
       </c>
@@ -2183,7 +2197,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:7" hidden="1">
+    <row r="63" spans="1:7">
       <c r="A63" s="3" t="s">
         <v>51</v>
       </c>
@@ -2206,7 +2220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:7" hidden="1">
+    <row r="64" spans="1:7">
       <c r="A64" s="3" t="s">
         <v>51</v>
       </c>
@@ -2229,7 +2243,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:7" hidden="1">
+    <row r="65" spans="1:7">
       <c r="A65" s="3" t="s">
         <v>51</v>
       </c>
@@ -2252,7 +2266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" hidden="1">
+    <row r="66" spans="1:7">
       <c r="A66" s="3" t="s">
         <v>51</v>
       </c>
@@ -2275,7 +2289,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:7" hidden="1">
+    <row r="67" spans="1:7">
       <c r="A67" s="3" t="s">
         <v>51</v>
       </c>
@@ -2298,7 +2312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:7" hidden="1">
+    <row r="68" spans="1:7">
       <c r="A68" s="3" t="s">
         <v>51</v>
       </c>
@@ -2321,7 +2335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" hidden="1">
+    <row r="69" spans="1:7">
       <c r="A69" s="3" t="s">
         <v>51</v>
       </c>
@@ -2344,7 +2358,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" hidden="1">
+    <row r="70" spans="1:7">
       <c r="A70" s="3" t="s">
         <v>51</v>
       </c>
@@ -2367,7 +2381,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" hidden="1">
+    <row r="71" spans="1:7">
       <c r="A71" s="3" t="s">
         <v>51</v>
       </c>
@@ -2390,7 +2404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:7" hidden="1">
+    <row r="72" spans="1:7">
       <c r="A72" s="3" t="s">
         <v>51</v>
       </c>
@@ -2413,7 +2427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:7" hidden="1">
+    <row r="73" spans="1:7">
       <c r="A73" s="3" t="s">
         <v>51</v>
       </c>
@@ -2436,7 +2450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" hidden="1">
+    <row r="74" spans="1:7">
       <c r="A74" s="3" t="s">
         <v>51</v>
       </c>
@@ -2459,7 +2473,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="75" spans="1:7" hidden="1">
+    <row r="75" spans="1:7">
       <c r="A75" s="3" t="s">
         <v>51</v>
       </c>
@@ -2482,7 +2496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="76" spans="1:7" hidden="1">
+    <row r="76" spans="1:7">
       <c r="A76" s="3" t="s">
         <v>51</v>
       </c>
@@ -2505,7 +2519,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="77" spans="1:7" hidden="1">
+    <row r="77" spans="1:7">
       <c r="A77" s="3" t="s">
         <v>51</v>
       </c>
@@ -2528,7 +2542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:7" hidden="1">
+    <row r="78" spans="1:7">
       <c r="A78" s="3" t="s">
         <v>51</v>
       </c>
@@ -2551,7 +2565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:7" hidden="1">
+    <row r="79" spans="1:7">
       <c r="A79" s="3" t="s">
         <v>51</v>
       </c>
@@ -2574,7 +2588,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="80" spans="1:7" hidden="1">
+    <row r="80" spans="1:7">
       <c r="A80" s="3" t="s">
         <v>51</v>
       </c>
@@ -2597,7 +2611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="81" spans="1:7" hidden="1">
+    <row r="81" spans="1:7">
       <c r="A81" s="3" t="s">
         <v>51</v>
       </c>
@@ -2620,7 +2634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="82" spans="1:7" hidden="1">
+    <row r="82" spans="1:7">
       <c r="A82" s="3" t="s">
         <v>51</v>
       </c>
@@ -2643,7 +2657,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:7" hidden="1">
+    <row r="83" spans="1:7">
       <c r="A83" s="3" t="s">
         <v>51</v>
       </c>
@@ -2666,7 +2680,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:7" hidden="1">
+    <row r="84" spans="1:7">
       <c r="A84" s="3" t="s">
         <v>51</v>
       </c>
@@ -2689,7 +2703,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:7" hidden="1">
+    <row r="85" spans="1:7">
       <c r="A85" s="3" t="s">
         <v>51</v>
       </c>
@@ -2712,7 +2726,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:7" hidden="1">
+    <row r="86" spans="1:7">
       <c r="A86" s="3" t="s">
         <v>51</v>
       </c>
@@ -2735,7 +2749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" hidden="1">
+    <row r="87" spans="1:7">
       <c r="A87" s="3" t="s">
         <v>51</v>
       </c>
@@ -2758,7 +2772,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="88" spans="1:7" hidden="1">
+    <row r="88" spans="1:7">
       <c r="A88" s="3" t="s">
         <v>51</v>
       </c>
@@ -2781,7 +2795,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" hidden="1">
+    <row r="89" spans="1:7">
       <c r="A89" s="3" t="s">
         <v>51</v>
       </c>
@@ -2804,7 +2818,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:7" hidden="1">
+    <row r="90" spans="1:7">
       <c r="A90" s="3" t="s">
         <v>51</v>
       </c>
@@ -2827,7 +2841,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:7" hidden="1">
+    <row r="91" spans="1:7">
       <c r="A91" s="3" t="s">
         <v>51</v>
       </c>
@@ -2850,7 +2864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:7" hidden="1">
+    <row r="92" spans="1:7">
       <c r="A92" s="3" t="s">
         <v>51</v>
       </c>
@@ -2873,7 +2887,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" hidden="1">
+    <row r="93" spans="1:7">
       <c r="A93" s="3" t="s">
         <v>51</v>
       </c>
@@ -2896,7 +2910,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:7" hidden="1">
+    <row r="94" spans="1:7">
       <c r="A94" s="3" t="s">
         <v>51</v>
       </c>
@@ -2919,7 +2933,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" hidden="1">
+    <row r="95" spans="1:7">
       <c r="A95" s="3" t="s">
         <v>51</v>
       </c>
@@ -2942,7 +2956,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="96" spans="1:7" hidden="1">
+    <row r="96" spans="1:7">
       <c r="A96" s="3" t="s">
         <v>51</v>
       </c>
@@ -2965,7 +2979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="97" spans="1:7" s="8" customFormat="1">
       <c r="A97" s="6" t="s">
         <v>61</v>
       </c>
@@ -2988,7 +3002,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" spans="1:7" hidden="1">
+    <row r="98" spans="1:7">
       <c r="A98" s="3" t="s">
         <v>61</v>
       </c>
@@ -3011,7 +3025,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" hidden="1">
+    <row r="99" spans="1:7">
       <c r="A99" s="3" t="s">
         <v>61</v>
       </c>
@@ -3034,7 +3048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="100" spans="1:7" hidden="1">
+    <row r="100" spans="1:7">
       <c r="A100" s="3" t="s">
         <v>61</v>
       </c>
@@ -3057,7 +3071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="101" spans="1:7" hidden="1">
+    <row r="101" spans="1:7">
       <c r="A101" s="3" t="s">
         <v>61</v>
       </c>
@@ -3080,7 +3094,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:7" hidden="1">
+    <row r="102" spans="1:7">
       <c r="A102" s="3" t="s">
         <v>61</v>
       </c>
@@ -3103,7 +3117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="103" spans="1:7" hidden="1">
+    <row r="103" spans="1:7">
       <c r="A103" s="3" t="s">
         <v>61</v>
       </c>
@@ -3126,7 +3140,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="104" spans="1:7" hidden="1">
+    <row r="104" spans="1:7">
       <c r="A104" s="3" t="s">
         <v>61</v>
       </c>
@@ -3149,7 +3163,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="105" spans="1:7" hidden="1">
+    <row r="105" spans="1:7">
       <c r="A105" s="3" t="s">
         <v>61</v>
       </c>
@@ -3172,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" hidden="1">
+    <row r="106" spans="1:7">
       <c r="A106" s="3" t="s">
         <v>61</v>
       </c>
@@ -3195,7 +3209,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" hidden="1">
+    <row r="107" spans="1:7">
       <c r="A107" s="3" t="s">
         <v>61</v>
       </c>
@@ -3218,7 +3232,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="108" spans="1:7" hidden="1">
+    <row r="108" spans="1:7">
       <c r="A108" s="3" t="s">
         <v>61</v>
       </c>
@@ -3241,7 +3255,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" hidden="1">
+    <row r="109" spans="1:7">
       <c r="A109" s="3" t="s">
         <v>61</v>
       </c>
@@ -3264,7 +3278,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="110" spans="1:7" hidden="1">
+    <row r="110" spans="1:7">
       <c r="A110" s="3" t="s">
         <v>61</v>
       </c>
@@ -3287,7 +3301,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="111" spans="1:7" hidden="1">
+    <row r="111" spans="1:7">
       <c r="A111" s="3" t="s">
         <v>61</v>
       </c>
@@ -3310,7 +3324,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:7" hidden="1">
+    <row r="112" spans="1:7">
       <c r="A112" s="3" t="s">
         <v>61</v>
       </c>
@@ -3333,7 +3347,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="113" spans="1:7" hidden="1">
+    <row r="113" spans="1:7">
       <c r="A113" s="3" t="s">
         <v>61</v>
       </c>
@@ -3356,7 +3370,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" hidden="1">
+    <row r="114" spans="1:7">
       <c r="A114" s="3" t="s">
         <v>61</v>
       </c>
@@ -3379,7 +3393,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" hidden="1">
+    <row r="115" spans="1:7">
       <c r="A115" s="3" t="s">
         <v>61</v>
       </c>
@@ -3402,7 +3416,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:7" hidden="1">
+    <row r="116" spans="1:7">
       <c r="A116" s="3" t="s">
         <v>61</v>
       </c>
@@ -3425,7 +3439,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:7" hidden="1">
+    <row r="117" spans="1:7">
       <c r="A117" s="3" t="s">
         <v>61</v>
       </c>
@@ -3448,7 +3462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:7" hidden="1">
+    <row r="118" spans="1:7">
       <c r="A118" s="3" t="s">
         <v>61</v>
       </c>
@@ -3471,7 +3485,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" hidden="1">
+    <row r="119" spans="1:7">
       <c r="A119" s="3" t="s">
         <v>61</v>
       </c>
@@ -3494,7 +3508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="120" spans="1:7" hidden="1">
+    <row r="120" spans="1:7">
       <c r="A120" s="3" t="s">
         <v>61</v>
       </c>
@@ -3517,7 +3531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="121" spans="1:7" hidden="1">
+    <row r="121" spans="1:7">
       <c r="A121" s="3" t="s">
         <v>61</v>
       </c>
@@ -3540,7 +3554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="122" spans="1:7" hidden="1">
+    <row r="122" spans="1:7">
       <c r="A122" s="3" t="s">
         <v>61</v>
       </c>
@@ -3563,7 +3577,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="123" spans="1:7" hidden="1">
+    <row r="123" spans="1:7">
       <c r="A123" s="3" t="s">
         <v>61</v>
       </c>
@@ -3586,7 +3600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:7" hidden="1">
+    <row r="124" spans="1:7">
       <c r="A124" s="3" t="s">
         <v>61</v>
       </c>
@@ -3609,7 +3623,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="125" spans="1:7" hidden="1">
+    <row r="125" spans="1:7">
       <c r="A125" s="3" t="s">
         <v>61</v>
       </c>
@@ -3632,7 +3646,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:7" hidden="1">
+    <row r="126" spans="1:7">
       <c r="A126" s="3" t="s">
         <v>61</v>
       </c>
@@ -3655,7 +3669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:7" hidden="1">
+    <row r="127" spans="1:7">
       <c r="A127" s="3" t="s">
         <v>61</v>
       </c>
@@ -3678,7 +3692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" hidden="1">
+    <row r="128" spans="1:7">
       <c r="A128" s="3" t="s">
         <v>61</v>
       </c>
@@ -3701,7 +3715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" hidden="1">
+    <row r="129" spans="1:7">
       <c r="A129" s="3" t="s">
         <v>61</v>
       </c>
@@ -3724,7 +3738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" hidden="1">
+    <row r="130" spans="1:7">
       <c r="A130" s="3" t="s">
         <v>61</v>
       </c>
@@ -3747,7 +3761,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="131" spans="1:7" hidden="1">
+    <row r="131" spans="1:7">
       <c r="A131" s="3" t="s">
         <v>61</v>
       </c>
@@ -3770,7 +3784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="1:7" hidden="1">
+    <row r="132" spans="1:7">
       <c r="A132" s="3" t="s">
         <v>61</v>
       </c>
@@ -3793,7 +3807,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="133" spans="1:7" s="8" customFormat="1">
       <c r="A133" s="6" t="s">
         <v>61</v>
       </c>
@@ -3816,7 +3830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="134" spans="1:7" hidden="1">
+    <row r="134" spans="1:7">
       <c r="A134" s="3" t="s">
         <v>61</v>
       </c>
@@ -3839,7 +3853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" hidden="1">
+    <row r="135" spans="1:7">
       <c r="A135" s="3" t="s">
         <v>61</v>
       </c>
@@ -3862,7 +3876,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:7" hidden="1">
+    <row r="136" spans="1:7">
       <c r="A136" s="3" t="s">
         <v>61</v>
       </c>
@@ -3885,7 +3899,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:7" hidden="1">
+    <row r="137" spans="1:7">
       <c r="A137" s="3" t="s">
         <v>61</v>
       </c>
@@ -3908,7 +3922,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="138" spans="1:7" hidden="1">
+    <row r="138" spans="1:7">
       <c r="A138" s="3" t="s">
         <v>61</v>
       </c>
@@ -3931,7 +3945,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="139" spans="1:7" hidden="1">
+    <row r="139" spans="1:7">
       <c r="A139" s="3" t="s">
         <v>61</v>
       </c>
@@ -3954,7 +3968,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="140" spans="1:7" hidden="1">
+    <row r="140" spans="1:7">
       <c r="A140" s="3" t="s">
         <v>61</v>
       </c>
@@ -3977,7 +3991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="141" spans="1:7" hidden="1">
+    <row r="141" spans="1:7">
       <c r="A141" s="3" t="s">
         <v>61</v>
       </c>
@@ -4000,7 +4014,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" hidden="1">
+    <row r="142" spans="1:7">
       <c r="A142" s="3" t="s">
         <v>61</v>
       </c>
@@ -4023,7 +4037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" hidden="1">
+    <row r="143" spans="1:7">
       <c r="A143" s="3" t="s">
         <v>61</v>
       </c>
@@ -4046,7 +4060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" hidden="1">
+    <row r="144" spans="1:7">
       <c r="A144" s="3" t="s">
         <v>61</v>
       </c>
@@ -4069,7 +4083,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" hidden="1">
+    <row r="145" spans="1:7">
       <c r="A145" s="3" t="s">
         <v>61</v>
       </c>
@@ -4092,7 +4106,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="146" spans="1:7" hidden="1">
+    <row r="146" spans="1:7">
       <c r="A146" s="3" t="s">
         <v>61</v>
       </c>
@@ -4115,7 +4129,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="147" spans="1:7" hidden="1">
+    <row r="147" spans="1:7">
       <c r="A147" s="3" t="s">
         <v>61</v>
       </c>
@@ -4138,7 +4152,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:7" hidden="1">
+    <row r="148" spans="1:7">
       <c r="A148" s="3" t="s">
         <v>61</v>
       </c>
@@ -4161,7 +4175,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="149" spans="1:7" hidden="1">
+    <row r="149" spans="1:7">
       <c r="A149" s="3" t="s">
         <v>61</v>
       </c>
@@ -4184,7 +4198,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="150" spans="1:7" hidden="1">
+    <row r="150" spans="1:7">
       <c r="A150" s="3" t="s">
         <v>61</v>
       </c>
@@ -4207,7 +4221,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" hidden="1">
+    <row r="151" spans="1:7">
       <c r="A151" s="3" t="s">
         <v>61</v>
       </c>
@@ -4230,7 +4244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" hidden="1">
+    <row r="152" spans="1:7">
       <c r="A152" s="3" t="s">
         <v>61</v>
       </c>
@@ -4253,7 +4267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" hidden="1">
+    <row r="153" spans="1:7">
       <c r="A153" s="3" t="s">
         <v>61</v>
       </c>
@@ -4276,7 +4290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" hidden="1">
+    <row r="154" spans="1:7">
       <c r="A154" s="3" t="s">
         <v>61</v>
       </c>
@@ -4299,7 +4313,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" hidden="1">
+    <row r="155" spans="1:7">
       <c r="A155" s="3" t="s">
         <v>61</v>
       </c>
@@ -4322,7 +4336,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:7" hidden="1">
+    <row r="156" spans="1:7">
       <c r="A156" s="3" t="s">
         <v>61</v>
       </c>
@@ -4345,7 +4359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:7" hidden="1">
+    <row r="157" spans="1:7">
       <c r="A157" s="3" t="s">
         <v>61</v>
       </c>
@@ -4368,7 +4382,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="158" spans="1:7" hidden="1">
+    <row r="158" spans="1:7">
       <c r="A158" s="3" t="s">
         <v>61</v>
       </c>
@@ -4391,7 +4405,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:7" hidden="1">
+    <row r="159" spans="1:7">
       <c r="A159" s="3" t="s">
         <v>61</v>
       </c>
@@ -4414,7 +4428,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:7" hidden="1">
+    <row r="160" spans="1:7">
       <c r="A160" s="3" t="s">
         <v>61</v>
       </c>
@@ -4437,7 +4451,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" hidden="1">
+    <row r="161" spans="1:7">
       <c r="A161" s="3" t="s">
         <v>61</v>
       </c>
@@ -4460,7 +4474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="162" spans="1:7" s="8" customFormat="1">
       <c r="A162" s="6" t="s">
         <v>61</v>
       </c>
@@ -4483,7 +4497,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:7" hidden="1">
+    <row r="163" spans="1:7">
       <c r="A163" s="3" t="s">
         <v>61</v>
       </c>
@@ -4506,7 +4520,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:7" hidden="1">
+    <row r="164" spans="1:7">
       <c r="A164" s="3" t="s">
         <v>61</v>
       </c>
@@ -4529,7 +4543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:7" hidden="1">
+    <row r="165" spans="1:7">
       <c r="A165" s="3" t="s">
         <v>61</v>
       </c>
@@ -4552,7 +4566,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="166" spans="1:7" hidden="1">
+    <row r="166" spans="1:7">
       <c r="A166" s="3" t="s">
         <v>61</v>
       </c>
@@ -4575,7 +4589,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" hidden="1">
+    <row r="167" spans="1:7">
       <c r="A167" s="3" t="s">
         <v>61</v>
       </c>
@@ -4598,7 +4612,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="168" spans="1:7" hidden="1">
+    <row r="168" spans="1:7">
       <c r="A168" s="3" t="s">
         <v>61</v>
       </c>
@@ -4621,7 +4635,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="169" spans="1:7" hidden="1">
+    <row r="169" spans="1:7">
       <c r="A169" s="3" t="s">
         <v>61</v>
       </c>
@@ -4644,7 +4658,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="170" spans="1:7" hidden="1">
+    <row r="170" spans="1:7">
       <c r="A170" s="3" t="s">
         <v>61</v>
       </c>
@@ -4667,7 +4681,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:7" hidden="1">
+    <row r="171" spans="1:7">
       <c r="A171" s="3" t="s">
         <v>61</v>
       </c>
@@ -4690,7 +4704,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:7" hidden="1">
+    <row r="172" spans="1:7">
       <c r="A172" s="3" t="s">
         <v>61</v>
       </c>
@@ -4713,7 +4727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="173" spans="1:7" hidden="1">
+    <row r="173" spans="1:7">
       <c r="A173" s="3" t="s">
         <v>61</v>
       </c>
@@ -4736,7 +4750,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:7" hidden="1">
+    <row r="174" spans="1:7">
       <c r="A174" s="3" t="s">
         <v>61</v>
       </c>
@@ -4759,7 +4773,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="175" spans="1:7" hidden="1">
+    <row r="175" spans="1:7">
       <c r="A175" s="3" t="s">
         <v>61</v>
       </c>
@@ -4782,7 +4796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="176" spans="1:7" hidden="1">
+    <row r="176" spans="1:7">
       <c r="A176" s="3" t="s">
         <v>61</v>
       </c>
@@ -4805,7 +4819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:7" hidden="1">
+    <row r="177" spans="1:7">
       <c r="A177" s="3" t="s">
         <v>61</v>
       </c>
@@ -4828,7 +4842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="178" spans="1:7" hidden="1">
+    <row r="178" spans="1:7">
       <c r="A178" s="3" t="s">
         <v>61</v>
       </c>
@@ -4851,7 +4865,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="179" spans="1:7" hidden="1">
+    <row r="179" spans="1:7">
       <c r="A179" s="3" t="s">
         <v>61</v>
       </c>
@@ -4874,7 +4888,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:7" hidden="1">
+    <row r="180" spans="1:7">
       <c r="A180" s="3" t="s">
         <v>61</v>
       </c>
@@ -4897,7 +4911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" hidden="1">
+    <row r="181" spans="1:7">
       <c r="A181" s="3" t="s">
         <v>61</v>
       </c>
@@ -4920,7 +4934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" hidden="1">
+    <row r="182" spans="1:7">
       <c r="A182" s="3" t="s">
         <v>61</v>
       </c>
@@ -4943,7 +4957,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" hidden="1">
+    <row r="183" spans="1:7">
       <c r="A183" s="3" t="s">
         <v>61</v>
       </c>
@@ -4966,7 +4980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" hidden="1">
+    <row r="184" spans="1:7">
       <c r="A184" s="3" t="s">
         <v>61</v>
       </c>
@@ -4989,7 +5003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="185" spans="1:7" hidden="1">
+    <row r="185" spans="1:7">
       <c r="A185" s="3" t="s">
         <v>61</v>
       </c>
@@ -5012,7 +5026,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:7" hidden="1">
+    <row r="186" spans="1:7">
       <c r="A186" s="3" t="s">
         <v>61</v>
       </c>
@@ -5035,7 +5049,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="187" spans="1:7" hidden="1">
+    <row r="187" spans="1:7">
       <c r="A187" s="3" t="s">
         <v>61</v>
       </c>
@@ -5058,7 +5072,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="188" spans="1:7" hidden="1">
+    <row r="188" spans="1:7">
       <c r="A188" s="3" t="s">
         <v>61</v>
       </c>
@@ -5081,7 +5095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" hidden="1">
+    <row r="189" spans="1:7">
       <c r="A189" s="3" t="s">
         <v>61</v>
       </c>
@@ -5104,7 +5118,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="190" spans="1:7" hidden="1">
+    <row r="190" spans="1:7">
       <c r="A190" s="3" t="s">
         <v>61</v>
       </c>
@@ -5127,7 +5141,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="191" spans="1:7" s="8" customFormat="1">
       <c r="A191" s="6" t="s">
         <v>61</v>
       </c>
@@ -5150,7 +5164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="192" spans="1:7" hidden="1">
+    <row r="192" spans="1:7">
       <c r="A192" s="3" t="s">
         <v>61</v>
       </c>
@@ -5173,7 +5187,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" hidden="1">
+    <row r="193" spans="1:7">
       <c r="A193" s="3" t="s">
         <v>61</v>
       </c>
@@ -5196,7 +5210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:7" hidden="1">
+    <row r="194" spans="1:7">
       <c r="A194" s="3" t="s">
         <v>61</v>
       </c>
@@ -5219,7 +5233,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="195" spans="1:7" hidden="1">
+    <row r="195" spans="1:7">
       <c r="A195" s="3" t="s">
         <v>61</v>
       </c>
@@ -5242,7 +5256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" hidden="1">
+    <row r="196" spans="1:7">
       <c r="A196" s="3" t="s">
         <v>61</v>
       </c>
@@ -5265,7 +5279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:7" hidden="1">
+    <row r="197" spans="1:7">
       <c r="A197" s="3" t="s">
         <v>61</v>
       </c>
@@ -5288,7 +5302,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" hidden="1">
+    <row r="198" spans="1:7">
       <c r="A198" s="3" t="s">
         <v>61</v>
       </c>
@@ -5311,7 +5325,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:7" hidden="1">
+    <row r="199" spans="1:7">
       <c r="A199" s="3" t="s">
         <v>61</v>
       </c>
@@ -5334,7 +5348,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" hidden="1">
+    <row r="200" spans="1:7">
       <c r="A200" s="3" t="s">
         <v>61</v>
       </c>
@@ -5357,7 +5371,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" hidden="1">
+    <row r="201" spans="1:7">
       <c r="A201" s="3" t="s">
         <v>61</v>
       </c>
@@ -5380,7 +5394,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:7" hidden="1">
+    <row r="202" spans="1:7">
       <c r="A202" s="3" t="s">
         <v>61</v>
       </c>
@@ -5403,7 +5417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" hidden="1">
+    <row r="203" spans="1:7">
       <c r="A203" s="3" t="s">
         <v>61</v>
       </c>
@@ -5426,7 +5440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="204" spans="1:7" hidden="1">
+    <row r="204" spans="1:7">
       <c r="A204" s="3" t="s">
         <v>61</v>
       </c>
@@ -5449,7 +5463,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="205" spans="1:7" hidden="1">
+    <row r="205" spans="1:7">
       <c r="A205" s="3" t="s">
         <v>61</v>
       </c>
@@ -5472,7 +5486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" hidden="1">
+    <row r="206" spans="1:7">
       <c r="A206" s="3" t="s">
         <v>61</v>
       </c>
@@ -5495,7 +5509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" hidden="1">
+    <row r="207" spans="1:7">
       <c r="A207" s="3" t="s">
         <v>61</v>
       </c>
@@ -5518,7 +5532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="208" spans="1:7" hidden="1">
+    <row r="208" spans="1:7">
       <c r="A208" s="3" t="s">
         <v>61</v>
       </c>
@@ -5541,7 +5555,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" hidden="1">
+    <row r="209" spans="1:7">
       <c r="A209" s="3" t="s">
         <v>61</v>
       </c>
@@ -5564,7 +5578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" hidden="1">
+    <row r="210" spans="1:7">
       <c r="A210" s="3" t="s">
         <v>61</v>
       </c>
@@ -5587,7 +5601,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:7" hidden="1">
+    <row r="211" spans="1:7">
       <c r="A211" s="3" t="s">
         <v>61</v>
       </c>
@@ -5610,7 +5624,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:7" hidden="1">
+    <row r="212" spans="1:7">
       <c r="A212" s="3" t="s">
         <v>61</v>
       </c>
@@ -5633,7 +5647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" hidden="1">
+    <row r="213" spans="1:7">
       <c r="A213" s="3" t="s">
         <v>61</v>
       </c>
@@ -5656,7 +5670,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="214" spans="1:7" hidden="1">
+    <row r="214" spans="1:7">
       <c r="A214" s="3" t="s">
         <v>61</v>
       </c>
@@ -5679,7 +5693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:7" hidden="1">
+    <row r="215" spans="1:7">
       <c r="A215" s="3" t="s">
         <v>61</v>
       </c>
@@ -5702,7 +5716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" hidden="1">
+    <row r="216" spans="1:7">
       <c r="A216" s="3" t="s">
         <v>61</v>
       </c>
@@ -5725,7 +5739,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="217" spans="1:7" hidden="1">
+    <row r="217" spans="1:7">
       <c r="A217" s="3" t="s">
         <v>61</v>
       </c>
@@ -5748,7 +5762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:7" hidden="1">
+    <row r="218" spans="1:7">
       <c r="A218" s="3" t="s">
         <v>61</v>
       </c>
@@ -5771,7 +5785,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="219" spans="1:7" hidden="1">
+    <row r="219" spans="1:7">
       <c r="A219" s="3" t="s">
         <v>61</v>
       </c>
@@ -5794,7 +5808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:7" hidden="1">
+    <row r="220" spans="1:7">
       <c r="A220" s="3" t="s">
         <v>61</v>
       </c>
@@ -5817,7 +5831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:7" hidden="1">
+    <row r="221" spans="1:7">
       <c r="A221" s="3" t="s">
         <v>61</v>
       </c>
@@ -5840,7 +5854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:7" hidden="1">
+    <row r="222" spans="1:7">
       <c r="A222" s="3" t="s">
         <v>61</v>
       </c>
@@ -5863,7 +5877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" hidden="1">
+    <row r="223" spans="1:7">
       <c r="A223" s="3" t="s">
         <v>61</v>
       </c>
@@ -5886,7 +5900,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:7" hidden="1">
+    <row r="224" spans="1:7">
       <c r="A224" s="3" t="s">
         <v>61</v>
       </c>
@@ -5909,7 +5923,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="225" spans="1:7" hidden="1">
+    <row r="225" spans="1:7">
       <c r="A225" s="3" t="s">
         <v>61</v>
       </c>
@@ -5932,7 +5946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="226" spans="1:7" hidden="1">
+    <row r="226" spans="1:7">
       <c r="A226" s="3" t="s">
         <v>61</v>
       </c>
@@ -5955,7 +5969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="227" spans="1:7" s="8" customFormat="1">
       <c r="A227" s="6" t="s">
         <v>61</v>
       </c>
@@ -5978,7 +5992,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="228" spans="1:7" hidden="1">
+    <row r="228" spans="1:7">
       <c r="A228" s="3" t="s">
         <v>61</v>
       </c>
@@ -6001,7 +6015,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:7" hidden="1">
+    <row r="229" spans="1:7">
       <c r="A229" s="3" t="s">
         <v>61</v>
       </c>
@@ -6024,7 +6038,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="230" spans="1:7" hidden="1">
+    <row r="230" spans="1:7">
       <c r="A230" s="3" t="s">
         <v>61</v>
       </c>
@@ -6047,7 +6061,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="231" spans="1:7" hidden="1">
+    <row r="231" spans="1:7">
       <c r="A231" s="3" t="s">
         <v>61</v>
       </c>
@@ -6070,7 +6084,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="232" spans="1:7" hidden="1">
+    <row r="232" spans="1:7">
       <c r="A232" s="3" t="s">
         <v>61</v>
       </c>
@@ -6093,7 +6107,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="233" spans="1:7" hidden="1">
+    <row r="233" spans="1:7">
       <c r="A233" s="3" t="s">
         <v>61</v>
       </c>
@@ -6116,7 +6130,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="234" spans="1:7" hidden="1">
+    <row r="234" spans="1:7">
       <c r="A234" s="3" t="s">
         <v>61</v>
       </c>
@@ -6139,7 +6153,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="235" spans="1:7" hidden="1">
+    <row r="235" spans="1:7">
       <c r="A235" s="3" t="s">
         <v>61</v>
       </c>
@@ -6162,7 +6176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:7" hidden="1">
+    <row r="236" spans="1:7">
       <c r="A236" s="3" t="s">
         <v>61</v>
       </c>
@@ -6185,7 +6199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:7" hidden="1">
+    <row r="237" spans="1:7">
       <c r="A237" s="3" t="s">
         <v>61</v>
       </c>
@@ -6208,7 +6222,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="238" spans="1:7" hidden="1">
+    <row r="238" spans="1:7">
       <c r="A238" s="3" t="s">
         <v>61</v>
       </c>
@@ -6231,7 +6245,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:7" hidden="1">
+    <row r="239" spans="1:7">
       <c r="A239" s="3" t="s">
         <v>61</v>
       </c>
@@ -6254,7 +6268,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="240" spans="1:7" hidden="1">
+    <row r="240" spans="1:7">
       <c r="A240" s="3" t="s">
         <v>61</v>
       </c>
@@ -6277,7 +6291,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="241" spans="1:7" hidden="1">
+    <row r="241" spans="1:7">
       <c r="A241" s="3" t="s">
         <v>61</v>
       </c>
@@ -6300,7 +6314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:7" hidden="1">
+    <row r="242" spans="1:7">
       <c r="A242" s="3" t="s">
         <v>61</v>
       </c>
@@ -6323,7 +6337,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="243" spans="1:7" hidden="1">
+    <row r="243" spans="1:7">
       <c r="A243" s="3" t="s">
         <v>61</v>
       </c>
@@ -6346,7 +6360,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:7" hidden="1">
+    <row r="244" spans="1:7">
       <c r="A244" s="3" t="s">
         <v>61</v>
       </c>
@@ -6369,7 +6383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" hidden="1">
+    <row r="245" spans="1:7">
       <c r="A245" s="3" t="s">
         <v>61</v>
       </c>
@@ -6392,7 +6406,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:7" hidden="1">
+    <row r="246" spans="1:7">
       <c r="A246" s="3" t="s">
         <v>61</v>
       </c>
@@ -6415,7 +6429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" hidden="1">
+    <row r="247" spans="1:7">
       <c r="A247" s="3" t="s">
         <v>61</v>
       </c>
@@ -6438,7 +6452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" hidden="1">
+    <row r="248" spans="1:7">
       <c r="A248" s="3" t="s">
         <v>61</v>
       </c>
@@ -6461,7 +6475,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" hidden="1">
+    <row r="249" spans="1:7">
       <c r="A249" s="3" t="s">
         <v>61</v>
       </c>
@@ -6484,7 +6498,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="250" spans="1:7" hidden="1">
+    <row r="250" spans="1:7">
       <c r="A250" s="3" t="s">
         <v>61</v>
       </c>
@@ -6507,7 +6521,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="251" spans="1:7" hidden="1">
+    <row r="251" spans="1:7">
       <c r="A251" s="3" t="s">
         <v>61</v>
       </c>
@@ -6530,7 +6544,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:7" hidden="1">
+    <row r="252" spans="1:7">
       <c r="A252" s="3" t="s">
         <v>61</v>
       </c>
@@ -6553,7 +6567,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="253" spans="1:7" hidden="1">
+    <row r="253" spans="1:7">
       <c r="A253" s="3" t="s">
         <v>61</v>
       </c>
@@ -6576,7 +6590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" hidden="1">
+    <row r="254" spans="1:7">
       <c r="A254" s="3" t="s">
         <v>61</v>
       </c>
@@ -6599,7 +6613,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="255" spans="1:7" hidden="1">
+    <row r="255" spans="1:7">
       <c r="A255" s="3" t="s">
         <v>61</v>
       </c>
@@ -6622,7 +6636,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="256" spans="1:7" s="8" customFormat="1">
       <c r="A256" s="6" t="s">
         <v>61</v>
       </c>
@@ -6645,7 +6659,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="257" spans="1:7" hidden="1">
+    <row r="257" spans="1:7">
       <c r="A257" s="3" t="s">
         <v>61</v>
       </c>
@@ -6668,7 +6682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:7" hidden="1">
+    <row r="258" spans="1:7">
       <c r="A258" s="3" t="s">
         <v>61</v>
       </c>
@@ -6691,7 +6705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" hidden="1">
+    <row r="259" spans="1:7">
       <c r="A259" s="3" t="s">
         <v>61</v>
       </c>
@@ -6714,7 +6728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="260" spans="1:7" hidden="1">
+    <row r="260" spans="1:7">
       <c r="A260" s="3" t="s">
         <v>61</v>
       </c>
@@ -6737,7 +6751,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="261" spans="1:7" hidden="1">
+    <row r="261" spans="1:7">
       <c r="A261" s="3" t="s">
         <v>61</v>
       </c>
@@ -6760,7 +6774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="262" spans="1:7" hidden="1">
+    <row r="262" spans="1:7">
       <c r="A262" s="3" t="s">
         <v>61</v>
       </c>
@@ -6783,7 +6797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:7" hidden="1">
+    <row r="263" spans="1:7">
       <c r="A263" s="3" t="s">
         <v>61</v>
       </c>
@@ -6806,7 +6820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="264" spans="1:7" hidden="1">
+    <row r="264" spans="1:7">
       <c r="A264" s="3" t="s">
         <v>61</v>
       </c>
@@ -6829,7 +6843,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:7" hidden="1">
+    <row r="265" spans="1:7">
       <c r="A265" s="3" t="s">
         <v>61</v>
       </c>
@@ -6852,7 +6866,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:7" hidden="1">
+    <row r="266" spans="1:7">
       <c r="A266" s="3" t="s">
         <v>61</v>
       </c>
@@ -6875,7 +6889,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:7" hidden="1">
+    <row r="267" spans="1:7">
       <c r="A267" s="3" t="s">
         <v>61</v>
       </c>
@@ -6898,7 +6912,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:7" hidden="1">
+    <row r="268" spans="1:7">
       <c r="A268" s="3" t="s">
         <v>61</v>
       </c>
@@ -6921,7 +6935,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="269" spans="1:7" hidden="1">
+    <row r="269" spans="1:7">
       <c r="A269" s="3" t="s">
         <v>61</v>
       </c>
@@ -6944,7 +6958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="270" spans="1:7" hidden="1">
+    <row r="270" spans="1:7">
       <c r="A270" s="3" t="s">
         <v>61</v>
       </c>
@@ -6967,7 +6981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="1:7" hidden="1">
+    <row r="271" spans="1:7">
       <c r="A271" s="3" t="s">
         <v>61</v>
       </c>
@@ -6990,7 +7004,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="272" spans="1:7" hidden="1">
+    <row r="272" spans="1:7">
       <c r="A272" s="3" t="s">
         <v>61</v>
       </c>
@@ -7013,7 +7027,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="273" spans="1:7" hidden="1">
+    <row r="273" spans="1:7">
       <c r="A273" s="3" t="s">
         <v>61</v>
       </c>
@@ -7036,7 +7050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:7" hidden="1">
+    <row r="274" spans="1:7">
       <c r="A274" s="3" t="s">
         <v>61</v>
       </c>
@@ -7059,7 +7073,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:7" hidden="1">
+    <row r="275" spans="1:7">
       <c r="A275" s="3" t="s">
         <v>61</v>
       </c>
@@ -7082,7 +7096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:7" hidden="1">
+    <row r="276" spans="1:7">
       <c r="A276" s="3" t="s">
         <v>61</v>
       </c>
@@ -7105,7 +7119,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:7" hidden="1">
+    <row r="277" spans="1:7">
       <c r="A277" s="3" t="s">
         <v>61</v>
       </c>
@@ -7128,7 +7142,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:7" hidden="1">
+    <row r="278" spans="1:7">
       <c r="A278" s="3" t="s">
         <v>61</v>
       </c>
@@ -7151,7 +7165,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="279" spans="1:7" hidden="1">
+    <row r="279" spans="1:7">
       <c r="A279" s="3" t="s">
         <v>61</v>
       </c>
@@ -7174,7 +7188,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="280" spans="1:7" hidden="1">
+    <row r="280" spans="1:7">
       <c r="A280" s="3" t="s">
         <v>61</v>
       </c>
@@ -7197,7 +7211,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="281" spans="1:7" hidden="1">
+    <row r="281" spans="1:7">
       <c r="A281" s="3" t="s">
         <v>61</v>
       </c>
@@ -7220,7 +7234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="282" spans="1:7" hidden="1">
+    <row r="282" spans="1:7">
       <c r="A282" s="3" t="s">
         <v>61</v>
       </c>
@@ -7243,7 +7257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:7" hidden="1">
+    <row r="283" spans="1:7">
       <c r="A283" s="3" t="s">
         <v>61</v>
       </c>
@@ -7266,7 +7280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="284" spans="1:7" hidden="1">
+    <row r="284" spans="1:7">
       <c r="A284" s="3" t="s">
         <v>61</v>
       </c>
@@ -7289,7 +7303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="285" spans="1:7" s="8" customFormat="1">
       <c r="A285" s="6" t="s">
         <v>61</v>
       </c>
@@ -7312,7 +7326,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:7" hidden="1">
+    <row r="286" spans="1:7">
       <c r="A286" s="3" t="s">
         <v>61</v>
       </c>
@@ -7335,7 +7349,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" hidden="1">
+    <row r="287" spans="1:7">
       <c r="A287" s="3" t="s">
         <v>61</v>
       </c>
@@ -7358,7 +7372,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="288" spans="1:7" hidden="1">
+    <row r="288" spans="1:7">
       <c r="A288" s="3" t="s">
         <v>61</v>
       </c>
@@ -7381,7 +7395,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="289" spans="1:7" hidden="1">
+    <row r="289" spans="1:7">
       <c r="A289" s="3" t="s">
         <v>61</v>
       </c>
@@ -7404,7 +7418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="290" spans="1:7" hidden="1">
+    <row r="290" spans="1:7">
       <c r="A290" s="3" t="s">
         <v>61</v>
       </c>
@@ -7427,7 +7441,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="291" spans="1:7" hidden="1">
+    <row r="291" spans="1:7">
       <c r="A291" s="3" t="s">
         <v>61</v>
       </c>
@@ -7450,7 +7464,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="292" spans="1:7" hidden="1">
+    <row r="292" spans="1:7">
       <c r="A292" s="3" t="s">
         <v>61</v>
       </c>
@@ -7473,7 +7487,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="293" spans="1:7" hidden="1">
+    <row r="293" spans="1:7">
       <c r="A293" s="3" t="s">
         <v>61</v>
       </c>
@@ -7496,7 +7510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" hidden="1">
+    <row r="294" spans="1:7">
       <c r="A294" s="3" t="s">
         <v>61</v>
       </c>
@@ -7519,7 +7533,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:7" hidden="1">
+    <row r="295" spans="1:7">
       <c r="A295" s="3" t="s">
         <v>61</v>
       </c>
@@ -7542,7 +7556,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="296" spans="1:7" hidden="1">
+    <row r="296" spans="1:7">
       <c r="A296" s="3" t="s">
         <v>61</v>
       </c>
@@ -7565,7 +7579,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:7" hidden="1">
+    <row r="297" spans="1:7">
       <c r="A297" s="3" t="s">
         <v>61</v>
       </c>
@@ -7588,7 +7602,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="298" spans="1:7" hidden="1">
+    <row r="298" spans="1:7">
       <c r="A298" s="3" t="s">
         <v>61</v>
       </c>
@@ -7611,7 +7625,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="299" spans="1:7" hidden="1">
+    <row r="299" spans="1:7">
       <c r="A299" s="3" t="s">
         <v>61</v>
       </c>
@@ -7634,7 +7648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:7" hidden="1">
+    <row r="300" spans="1:7">
       <c r="A300" s="3" t="s">
         <v>61</v>
       </c>
@@ -7657,7 +7671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="301" spans="1:7" hidden="1">
+    <row r="301" spans="1:7">
       <c r="A301" s="3" t="s">
         <v>61</v>
       </c>
@@ -7680,7 +7694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="302" spans="1:7" hidden="1">
+    <row r="302" spans="1:7">
       <c r="A302" s="3" t="s">
         <v>61</v>
       </c>
@@ -7703,7 +7717,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" hidden="1">
+    <row r="303" spans="1:7">
       <c r="A303" s="3" t="s">
         <v>61</v>
       </c>
@@ -7726,7 +7740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:7" hidden="1">
+    <row r="304" spans="1:7">
       <c r="A304" s="3" t="s">
         <v>61</v>
       </c>
@@ -7749,7 +7763,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" hidden="1">
+    <row r="305" spans="1:7">
       <c r="A305" s="3" t="s">
         <v>61</v>
       </c>
@@ -7772,7 +7786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:7" hidden="1">
+    <row r="306" spans="1:7">
       <c r="A306" s="3" t="s">
         <v>61</v>
       </c>
@@ -7795,7 +7809,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" hidden="1">
+    <row r="307" spans="1:7">
       <c r="A307" s="3" t="s">
         <v>61</v>
       </c>
@@ -7818,7 +7832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="308" spans="1:7" hidden="1">
+    <row r="308" spans="1:7">
       <c r="A308" s="3" t="s">
         <v>61</v>
       </c>
@@ -7841,7 +7855,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="309" spans="1:7" hidden="1">
+    <row r="309" spans="1:7">
       <c r="A309" s="3" t="s">
         <v>61</v>
       </c>
@@ -7864,7 +7878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="310" spans="1:7" hidden="1">
+    <row r="310" spans="1:7">
       <c r="A310" s="3" t="s">
         <v>61</v>
       </c>
@@ -7887,7 +7901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="311" spans="1:7" hidden="1">
+    <row r="311" spans="1:7">
       <c r="A311" s="3" t="s">
         <v>61</v>
       </c>
@@ -7910,7 +7924,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:7" hidden="1">
+    <row r="312" spans="1:7">
       <c r="A312" s="3" t="s">
         <v>61</v>
       </c>
@@ -7933,7 +7947,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="313" spans="1:7" hidden="1">
+    <row r="313" spans="1:7">
       <c r="A313" s="3" t="s">
         <v>61</v>
       </c>
@@ -7956,7 +7970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="314" spans="1:7" s="8" customFormat="1">
       <c r="A314" s="6" t="s">
         <v>61</v>
       </c>
@@ -7979,7 +7993,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="315" spans="1:7" hidden="1">
+    <row r="315" spans="1:7">
       <c r="A315" s="3" t="s">
         <v>61</v>
       </c>
@@ -8002,7 +8016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="316" spans="1:7" hidden="1">
+    <row r="316" spans="1:7">
       <c r="A316" s="3" t="s">
         <v>61</v>
       </c>
@@ -8025,7 +8039,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="317" spans="1:7" hidden="1">
+    <row r="317" spans="1:7">
       <c r="A317" s="3" t="s">
         <v>61</v>
       </c>
@@ -8048,7 +8062,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="318" spans="1:7" hidden="1">
+    <row r="318" spans="1:7">
       <c r="A318" s="3" t="s">
         <v>61</v>
       </c>
@@ -8071,7 +8085,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="319" spans="1:7" hidden="1">
+    <row r="319" spans="1:7">
       <c r="A319" s="3" t="s">
         <v>61</v>
       </c>
@@ -8094,7 +8108,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="320" spans="1:7" hidden="1">
+    <row r="320" spans="1:7">
       <c r="A320" s="3" t="s">
         <v>61</v>
       </c>
@@ -8117,7 +8131,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="321" spans="1:7" hidden="1">
+    <row r="321" spans="1:7">
       <c r="A321" s="3" t="s">
         <v>61</v>
       </c>
@@ -8140,7 +8154,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="322" spans="1:7" hidden="1">
+    <row r="322" spans="1:7">
       <c r="A322" s="3" t="s">
         <v>61</v>
       </c>
@@ -8163,7 +8177,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="323" spans="1:7" hidden="1">
+    <row r="323" spans="1:7">
       <c r="A323" s="3" t="s">
         <v>61</v>
       </c>
@@ -8186,7 +8200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" hidden="1">
+    <row r="324" spans="1:7">
       <c r="A324" s="3" t="s">
         <v>61</v>
       </c>
@@ -8209,7 +8223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="325" spans="1:7" hidden="1">
+    <row r="325" spans="1:7">
       <c r="A325" s="3" t="s">
         <v>61</v>
       </c>
@@ -8232,7 +8246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="326" spans="1:7" hidden="1">
+    <row r="326" spans="1:7">
       <c r="A326" s="3" t="s">
         <v>61</v>
       </c>
@@ -8255,7 +8269,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="327" spans="1:7" hidden="1">
+    <row r="327" spans="1:7">
       <c r="A327" s="3" t="s">
         <v>61</v>
       </c>
@@ -8278,7 +8292,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="328" spans="1:7" hidden="1">
+    <row r="328" spans="1:7">
       <c r="A328" s="3" t="s">
         <v>61</v>
       </c>
@@ -8301,7 +8315,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="329" spans="1:7" hidden="1">
+    <row r="329" spans="1:7">
       <c r="A329" s="3" t="s">
         <v>61</v>
       </c>
@@ -8324,7 +8338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:7" hidden="1">
+    <row r="330" spans="1:7">
       <c r="A330" s="3" t="s">
         <v>61</v>
       </c>
@@ -8347,7 +8361,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="331" spans="1:7" hidden="1">
+    <row r="331" spans="1:7">
       <c r="A331" s="3" t="s">
         <v>61</v>
       </c>
@@ -8370,7 +8384,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="332" spans="1:7" hidden="1">
+    <row r="332" spans="1:7">
       <c r="A332" s="3" t="s">
         <v>61</v>
       </c>
@@ -8393,7 +8407,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="333" spans="1:7" hidden="1">
+    <row r="333" spans="1:7">
       <c r="A333" s="3" t="s">
         <v>61</v>
       </c>
@@ -8416,7 +8430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="334" spans="1:7" hidden="1">
+    <row r="334" spans="1:7">
       <c r="A334" s="3" t="s">
         <v>61</v>
       </c>
@@ -8439,7 +8453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="335" spans="1:7" hidden="1">
+    <row r="335" spans="1:7">
       <c r="A335" s="3" t="s">
         <v>61</v>
       </c>
@@ -8462,7 +8476,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="336" spans="1:7" hidden="1">
+    <row r="336" spans="1:7">
       <c r="A336" s="3" t="s">
         <v>61</v>
       </c>
@@ -8485,7 +8499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="337" spans="1:7" hidden="1">
+    <row r="337" spans="1:7">
       <c r="A337" s="3" t="s">
         <v>61</v>
       </c>
@@ -8508,7 +8522,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="338" spans="1:7" hidden="1">
+    <row r="338" spans="1:7">
       <c r="A338" s="3" t="s">
         <v>61</v>
       </c>
@@ -8531,7 +8545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="339" spans="1:7" hidden="1">
+    <row r="339" spans="1:7">
       <c r="A339" s="3" t="s">
         <v>61</v>
       </c>
@@ -8554,7 +8568,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:7" hidden="1">
+    <row r="340" spans="1:7">
       <c r="A340" s="3" t="s">
         <v>61</v>
       </c>
@@ -8577,7 +8591,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="341" spans="1:7" hidden="1">
+    <row r="341" spans="1:7">
       <c r="A341" s="3" t="s">
         <v>61</v>
       </c>
@@ -8600,7 +8614,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="342" spans="1:7" hidden="1">
+    <row r="342" spans="1:7">
       <c r="A342" s="3" t="s">
         <v>61</v>
       </c>
@@ -8623,7 +8637,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="343" spans="1:7" hidden="1">
+    <row r="343" spans="1:7">
       <c r="A343" s="3" t="s">
         <v>61</v>
       </c>
@@ -8646,7 +8660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="344" spans="1:7" hidden="1">
+    <row r="344" spans="1:7">
       <c r="A344" s="3" t="s">
         <v>61</v>
       </c>
@@ -8669,7 +8683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="345" spans="1:7" hidden="1">
+    <row r="345" spans="1:7">
       <c r="A345" s="3" t="s">
         <v>61</v>
       </c>
@@ -8692,7 +8706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="346" spans="1:7" hidden="1">
+    <row r="346" spans="1:7">
       <c r="A346" s="3" t="s">
         <v>61</v>
       </c>
@@ -8715,7 +8729,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="347" spans="1:7" hidden="1">
+    <row r="347" spans="1:7">
       <c r="A347" s="3" t="s">
         <v>61</v>
       </c>
@@ -8738,7 +8752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="348" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="348" spans="1:7" s="8" customFormat="1">
       <c r="A348" s="6" t="s">
         <v>61</v>
       </c>
@@ -8761,7 +8775,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="349" spans="1:7" hidden="1">
+    <row r="349" spans="1:7">
       <c r="A349" s="3" t="s">
         <v>61</v>
       </c>
@@ -8784,7 +8798,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="350" spans="1:7" hidden="1">
+    <row r="350" spans="1:7">
       <c r="A350" s="3" t="s">
         <v>61</v>
       </c>
@@ -8807,7 +8821,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="351" spans="1:7" hidden="1">
+    <row r="351" spans="1:7">
       <c r="A351" s="3" t="s">
         <v>61</v>
       </c>
@@ -8830,7 +8844,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="352" spans="1:7" hidden="1">
+    <row r="352" spans="1:7">
       <c r="A352" s="3" t="s">
         <v>61</v>
       </c>
@@ -8853,7 +8867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="353" spans="1:7" hidden="1">
+    <row r="353" spans="1:7">
       <c r="A353" s="3" t="s">
         <v>61</v>
       </c>
@@ -8876,7 +8890,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="354" spans="1:7" hidden="1">
+    <row r="354" spans="1:7">
       <c r="A354" s="3" t="s">
         <v>61</v>
       </c>
@@ -8899,7 +8913,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="355" spans="1:7" hidden="1">
+    <row r="355" spans="1:7">
       <c r="A355" s="3" t="s">
         <v>61</v>
       </c>
@@ -8922,7 +8936,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="356" spans="1:7" hidden="1">
+    <row r="356" spans="1:7">
       <c r="A356" s="3" t="s">
         <v>61</v>
       </c>
@@ -8945,7 +8959,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="357" spans="1:7" hidden="1">
+    <row r="357" spans="1:7">
       <c r="A357" s="3" t="s">
         <v>61</v>
       </c>
@@ -8968,7 +8982,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="358" spans="1:7" hidden="1">
+    <row r="358" spans="1:7">
       <c r="A358" s="3" t="s">
         <v>61</v>
       </c>
@@ -8991,7 +9005,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="359" spans="1:7" hidden="1">
+    <row r="359" spans="1:7">
       <c r="A359" s="3" t="s">
         <v>61</v>
       </c>
@@ -9014,7 +9028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="360" spans="1:7" hidden="1">
+    <row r="360" spans="1:7">
       <c r="A360" s="3" t="s">
         <v>61</v>
       </c>
@@ -9037,7 +9051,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="361" spans="1:7" hidden="1">
+    <row r="361" spans="1:7">
       <c r="A361" s="3" t="s">
         <v>61</v>
       </c>
@@ -9060,7 +9074,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="362" spans="1:7" hidden="1">
+    <row r="362" spans="1:7">
       <c r="A362" s="3" t="s">
         <v>61</v>
       </c>
@@ -9083,7 +9097,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="363" spans="1:7" hidden="1">
+    <row r="363" spans="1:7">
       <c r="A363" s="3" t="s">
         <v>61</v>
       </c>
@@ -9106,7 +9120,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="364" spans="1:7" hidden="1">
+    <row r="364" spans="1:7">
       <c r="A364" s="3" t="s">
         <v>61</v>
       </c>
@@ -9129,7 +9143,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="365" spans="1:7" hidden="1">
+    <row r="365" spans="1:7">
       <c r="A365" s="3" t="s">
         <v>61</v>
       </c>
@@ -9152,7 +9166,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="366" spans="1:7" hidden="1">
+    <row r="366" spans="1:7">
       <c r="A366" s="3" t="s">
         <v>61</v>
       </c>
@@ -9175,7 +9189,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" hidden="1">
+    <row r="367" spans="1:7">
       <c r="A367" s="3" t="s">
         <v>61</v>
       </c>
@@ -9198,7 +9212,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="368" spans="1:7" hidden="1">
+    <row r="368" spans="1:7">
       <c r="A368" s="3" t="s">
         <v>61</v>
       </c>
@@ -9221,7 +9235,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" hidden="1">
+    <row r="369" spans="1:7">
       <c r="A369" s="3" t="s">
         <v>61</v>
       </c>
@@ -9244,7 +9258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="370" spans="1:7" hidden="1">
+    <row r="370" spans="1:7">
       <c r="A370" s="3" t="s">
         <v>61</v>
       </c>
@@ -9267,7 +9281,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="371" spans="1:7" hidden="1">
+    <row r="371" spans="1:7">
       <c r="A371" s="3" t="s">
         <v>61</v>
       </c>
@@ -9290,7 +9304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="372" spans="1:7" hidden="1">
+    <row r="372" spans="1:7">
       <c r="A372" s="3" t="s">
         <v>61</v>
       </c>
@@ -9313,7 +9327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="373" spans="1:7" hidden="1">
+    <row r="373" spans="1:7">
       <c r="A373" s="3" t="s">
         <v>61</v>
       </c>
@@ -9336,7 +9350,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="374" spans="1:7" hidden="1">
+    <row r="374" spans="1:7">
       <c r="A374" s="3" t="s">
         <v>61</v>
       </c>
@@ -9359,7 +9373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" hidden="1">
+    <row r="375" spans="1:7">
       <c r="A375" s="3" t="s">
         <v>61</v>
       </c>
@@ -9382,7 +9396,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="376" spans="1:7" hidden="1">
+    <row r="376" spans="1:7">
       <c r="A376" s="3" t="s">
         <v>61</v>
       </c>
@@ -9405,7 +9419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="377" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="377" spans="1:7" s="8" customFormat="1">
       <c r="A377" s="6" t="s">
         <v>61</v>
       </c>
@@ -9428,7 +9442,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="378" spans="1:7" hidden="1">
+    <row r="378" spans="1:7">
       <c r="A378" s="3" t="s">
         <v>61</v>
       </c>
@@ -9451,7 +9465,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" hidden="1">
+    <row r="379" spans="1:7">
       <c r="A379" s="3" t="s">
         <v>61</v>
       </c>
@@ -9474,7 +9488,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="380" spans="1:7" hidden="1">
+    <row r="380" spans="1:7">
       <c r="A380" s="3" t="s">
         <v>61</v>
       </c>
@@ -9497,7 +9511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="381" spans="1:7" hidden="1">
+    <row r="381" spans="1:7">
       <c r="A381" s="3" t="s">
         <v>61</v>
       </c>
@@ -9520,7 +9534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="382" spans="1:7" hidden="1">
+    <row r="382" spans="1:7">
       <c r="A382" s="3" t="s">
         <v>61</v>
       </c>
@@ -9543,7 +9557,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="383" spans="1:7" hidden="1">
+    <row r="383" spans="1:7">
       <c r="A383" s="3" t="s">
         <v>61</v>
       </c>
@@ -9566,7 +9580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="384" spans="1:7" hidden="1">
+    <row r="384" spans="1:7">
       <c r="A384" s="3" t="s">
         <v>61</v>
       </c>
@@ -9589,7 +9603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="385" spans="1:7" hidden="1">
+    <row r="385" spans="1:7">
       <c r="A385" s="3" t="s">
         <v>61</v>
       </c>
@@ -9612,7 +9626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="386" spans="1:7" hidden="1">
+    <row r="386" spans="1:7">
       <c r="A386" s="3" t="s">
         <v>61</v>
       </c>
@@ -9635,7 +9649,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="387" spans="1:7" hidden="1">
+    <row r="387" spans="1:7">
       <c r="A387" s="3" t="s">
         <v>61</v>
       </c>
@@ -9658,7 +9672,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="388" spans="1:7" hidden="1">
+    <row r="388" spans="1:7">
       <c r="A388" s="3" t="s">
         <v>61</v>
       </c>
@@ -9681,7 +9695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="389" spans="1:7" hidden="1">
+    <row r="389" spans="1:7">
       <c r="A389" s="3" t="s">
         <v>61</v>
       </c>
@@ -9704,7 +9718,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="390" spans="1:7" hidden="1">
+    <row r="390" spans="1:7">
       <c r="A390" s="3" t="s">
         <v>61</v>
       </c>
@@ -9727,7 +9741,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="391" spans="1:7" hidden="1">
+    <row r="391" spans="1:7">
       <c r="A391" s="3" t="s">
         <v>61</v>
       </c>
@@ -9750,7 +9764,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" hidden="1">
+    <row r="392" spans="1:7">
       <c r="A392" s="3" t="s">
         <v>61</v>
       </c>
@@ -9773,7 +9787,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="393" spans="1:7" hidden="1">
+    <row r="393" spans="1:7">
       <c r="A393" s="3" t="s">
         <v>61</v>
       </c>
@@ -9796,7 +9810,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="394" spans="1:7" hidden="1">
+    <row r="394" spans="1:7">
       <c r="A394" s="3" t="s">
         <v>61</v>
       </c>
@@ -9819,7 +9833,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="395" spans="1:7" hidden="1">
+    <row r="395" spans="1:7">
       <c r="A395" s="3" t="s">
         <v>61</v>
       </c>
@@ -9842,7 +9856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="396" spans="1:7" hidden="1">
+    <row r="396" spans="1:7">
       <c r="A396" s="3" t="s">
         <v>61</v>
       </c>
@@ -9865,7 +9879,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="397" spans="1:7" hidden="1">
+    <row r="397" spans="1:7">
       <c r="A397" s="3" t="s">
         <v>61</v>
       </c>
@@ -9888,7 +9902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="398" spans="1:7" hidden="1">
+    <row r="398" spans="1:7">
       <c r="A398" s="3" t="s">
         <v>61</v>
       </c>
@@ -9911,7 +9925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="399" spans="1:7" hidden="1">
+    <row r="399" spans="1:7">
       <c r="A399" s="3" t="s">
         <v>61</v>
       </c>
@@ -9934,7 +9948,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="400" spans="1:7" hidden="1">
+    <row r="400" spans="1:7">
       <c r="A400" s="3" t="s">
         <v>61</v>
       </c>
@@ -9957,7 +9971,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="401" spans="1:7" hidden="1">
+    <row r="401" spans="1:7">
       <c r="A401" s="3" t="s">
         <v>61</v>
       </c>
@@ -9980,7 +9994,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="402" spans="1:7" hidden="1">
+    <row r="402" spans="1:7">
       <c r="A402" s="3" t="s">
         <v>61</v>
       </c>
@@ -10003,7 +10017,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="403" spans="1:7" hidden="1">
+    <row r="403" spans="1:7">
       <c r="A403" s="3" t="s">
         <v>61</v>
       </c>
@@ -10026,7 +10040,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="404" spans="1:7" hidden="1">
+    <row r="404" spans="1:7">
       <c r="A404" s="3" t="s">
         <v>61</v>
       </c>
@@ -10049,7 +10063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="405" spans="1:7" hidden="1">
+    <row r="405" spans="1:7">
       <c r="A405" s="3" t="s">
         <v>61</v>
       </c>
@@ -10072,7 +10086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="406" spans="1:7" hidden="1">
+    <row r="406" spans="1:7">
       <c r="A406" s="3" t="s">
         <v>61</v>
       </c>
@@ -10095,7 +10109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="407" spans="1:7" hidden="1">
+    <row r="407" spans="1:7">
       <c r="A407" s="3" t="s">
         <v>61</v>
       </c>
@@ -10118,7 +10132,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="408" spans="1:7" hidden="1">
+    <row r="408" spans="1:7">
       <c r="A408" s="3" t="s">
         <v>61</v>
       </c>
@@ -10141,7 +10155,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="409" spans="1:7" hidden="1">
+    <row r="409" spans="1:7">
       <c r="A409" s="3" t="s">
         <v>61</v>
       </c>
@@ -10164,7 +10178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="410" spans="1:7" hidden="1">
+    <row r="410" spans="1:7">
       <c r="A410" s="3" t="s">
         <v>61</v>
       </c>
@@ -10187,7 +10201,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="411" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="411" spans="1:7" s="8" customFormat="1">
       <c r="A411" s="6" t="s">
         <v>61</v>
       </c>
@@ -10210,7 +10224,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="412" spans="1:7" hidden="1">
+    <row r="412" spans="1:7">
       <c r="A412" s="3" t="s">
         <v>61</v>
       </c>
@@ -10233,7 +10247,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="413" spans="1:7" hidden="1">
+    <row r="413" spans="1:7">
       <c r="A413" s="3" t="s">
         <v>61</v>
       </c>
@@ -10256,7 +10270,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="414" spans="1:7" hidden="1">
+    <row r="414" spans="1:7">
       <c r="A414" s="3" t="s">
         <v>61</v>
       </c>
@@ -10279,7 +10293,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="415" spans="1:7" hidden="1">
+    <row r="415" spans="1:7">
       <c r="A415" s="3" t="s">
         <v>61</v>
       </c>
@@ -10302,7 +10316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="416" spans="1:7" hidden="1">
+    <row r="416" spans="1:7">
       <c r="A416" s="3" t="s">
         <v>61</v>
       </c>
@@ -10325,7 +10339,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="417" spans="1:7" hidden="1">
+    <row r="417" spans="1:7">
       <c r="A417" s="3" t="s">
         <v>61</v>
       </c>
@@ -10348,7 +10362,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="418" spans="1:7" hidden="1">
+    <row r="418" spans="1:7">
       <c r="A418" s="3" t="s">
         <v>61</v>
       </c>
@@ -10371,7 +10385,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="419" spans="1:7" hidden="1">
+    <row r="419" spans="1:7">
       <c r="A419" s="3" t="s">
         <v>61</v>
       </c>
@@ -10394,7 +10408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" hidden="1">
+    <row r="420" spans="1:7">
       <c r="A420" s="3" t="s">
         <v>61</v>
       </c>
@@ -10417,7 +10431,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="421" spans="1:7" hidden="1">
+    <row r="421" spans="1:7">
       <c r="A421" s="3" t="s">
         <v>61</v>
       </c>
@@ -10440,7 +10454,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="422" spans="1:7" hidden="1">
+    <row r="422" spans="1:7">
       <c r="A422" s="3" t="s">
         <v>61</v>
       </c>
@@ -10463,7 +10477,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="423" spans="1:7" hidden="1">
+    <row r="423" spans="1:7">
       <c r="A423" s="3" t="s">
         <v>61</v>
       </c>
@@ -10486,7 +10500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="424" spans="1:7" hidden="1">
+    <row r="424" spans="1:7">
       <c r="A424" s="3" t="s">
         <v>61</v>
       </c>
@@ -10509,7 +10523,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="425" spans="1:7" hidden="1">
+    <row r="425" spans="1:7">
       <c r="A425" s="3" t="s">
         <v>61</v>
       </c>
@@ -10532,7 +10546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="426" spans="1:7" hidden="1">
+    <row r="426" spans="1:7">
       <c r="A426" s="3" t="s">
         <v>61</v>
       </c>
@@ -10555,7 +10569,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="427" spans="1:7" hidden="1">
+    <row r="427" spans="1:7">
       <c r="A427" s="3" t="s">
         <v>61</v>
       </c>
@@ -10578,7 +10592,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="428" spans="1:7" hidden="1">
+    <row r="428" spans="1:7">
       <c r="A428" s="3" t="s">
         <v>61</v>
       </c>
@@ -10601,7 +10615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="429" spans="1:7" hidden="1">
+    <row r="429" spans="1:7">
       <c r="A429" s="3" t="s">
         <v>61</v>
       </c>
@@ -10624,7 +10638,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="430" spans="1:7" hidden="1">
+    <row r="430" spans="1:7">
       <c r="A430" s="3" t="s">
         <v>61</v>
       </c>
@@ -10647,7 +10661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="431" spans="1:7" hidden="1">
+    <row r="431" spans="1:7">
       <c r="A431" s="3" t="s">
         <v>61</v>
       </c>
@@ -10670,7 +10684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="432" spans="1:7" hidden="1">
+    <row r="432" spans="1:7">
       <c r="A432" s="3" t="s">
         <v>61</v>
       </c>
@@ -10693,7 +10707,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="433" spans="1:7" hidden="1">
+    <row r="433" spans="1:7">
       <c r="A433" s="3" t="s">
         <v>61</v>
       </c>
@@ -10716,7 +10730,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="434" spans="1:7" hidden="1">
+    <row r="434" spans="1:7">
       <c r="A434" s="3" t="s">
         <v>61</v>
       </c>
@@ -10739,7 +10753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="435" spans="1:7" hidden="1">
+    <row r="435" spans="1:7">
       <c r="A435" s="3" t="s">
         <v>61</v>
       </c>
@@ -10762,7 +10776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="436" spans="1:7" hidden="1">
+    <row r="436" spans="1:7">
       <c r="A436" s="3" t="s">
         <v>61</v>
       </c>
@@ -10785,7 +10799,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="437" spans="1:7" hidden="1">
+    <row r="437" spans="1:7">
       <c r="A437" s="3" t="s">
         <v>61</v>
       </c>
@@ -10808,7 +10822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="438" spans="1:7" hidden="1">
+    <row r="438" spans="1:7">
       <c r="A438" s="3" t="s">
         <v>61</v>
       </c>
@@ -10831,7 +10845,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="439" spans="1:7" hidden="1">
+    <row r="439" spans="1:7">
       <c r="A439" s="3" t="s">
         <v>61</v>
       </c>
@@ -10854,7 +10868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="440" spans="1:7" hidden="1">
+    <row r="440" spans="1:7">
       <c r="A440" s="3" t="s">
         <v>61</v>
       </c>
@@ -10877,7 +10891,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="441" spans="1:7" hidden="1">
+    <row r="441" spans="1:7">
       <c r="A441" s="3" t="s">
         <v>61</v>
       </c>
@@ -10900,7 +10914,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="442" spans="1:7" hidden="1">
+    <row r="442" spans="1:7">
       <c r="A442" s="3" t="s">
         <v>61</v>
       </c>
@@ -10923,7 +10937,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="443" spans="1:7" hidden="1">
+    <row r="443" spans="1:7">
       <c r="A443" s="3" t="s">
         <v>61</v>
       </c>
@@ -10946,7 +10960,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="444" spans="1:7" hidden="1">
+    <row r="444" spans="1:7">
       <c r="A444" s="3" t="s">
         <v>61</v>
       </c>
@@ -10969,7 +10983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="445" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="445" spans="1:7" s="8" customFormat="1">
       <c r="A445" s="6" t="s">
         <v>61</v>
       </c>
@@ -10992,7 +11006,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="446" spans="1:7" hidden="1">
+    <row r="446" spans="1:7">
       <c r="A446" s="3" t="s">
         <v>61</v>
       </c>
@@ -11015,7 +11029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="447" spans="1:7" hidden="1">
+    <row r="447" spans="1:7">
       <c r="A447" s="3" t="s">
         <v>61</v>
       </c>
@@ -11038,7 +11052,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="448" spans="1:7" hidden="1">
+    <row r="448" spans="1:7">
       <c r="A448" s="3" t="s">
         <v>61</v>
       </c>
@@ -11061,7 +11075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="449" spans="1:7" hidden="1">
+    <row r="449" spans="1:7">
       <c r="A449" s="3" t="s">
         <v>61</v>
       </c>
@@ -11084,7 +11098,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="450" spans="1:7" hidden="1">
+    <row r="450" spans="1:7">
       <c r="A450" s="3" t="s">
         <v>61</v>
       </c>
@@ -11107,7 +11121,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="451" spans="1:7" hidden="1">
+    <row r="451" spans="1:7">
       <c r="A451" s="3" t="s">
         <v>61</v>
       </c>
@@ -11130,7 +11144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="452" spans="1:7" hidden="1">
+    <row r="452" spans="1:7">
       <c r="A452" s="3" t="s">
         <v>61</v>
       </c>
@@ -11153,7 +11167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="453" spans="1:7" hidden="1">
+    <row r="453" spans="1:7">
       <c r="A453" s="3" t="s">
         <v>61</v>
       </c>
@@ -11176,7 +11190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="454" spans="1:7" hidden="1">
+    <row r="454" spans="1:7">
       <c r="A454" s="3" t="s">
         <v>61</v>
       </c>
@@ -11199,7 +11213,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" hidden="1">
+    <row r="455" spans="1:7">
       <c r="A455" s="3" t="s">
         <v>61</v>
       </c>
@@ -11222,7 +11236,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="456" spans="1:7" hidden="1">
+    <row r="456" spans="1:7">
       <c r="A456" s="3" t="s">
         <v>61</v>
       </c>
@@ -11245,7 +11259,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" hidden="1">
+    <row r="457" spans="1:7">
       <c r="A457" s="3" t="s">
         <v>61</v>
       </c>
@@ -11268,7 +11282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="458" spans="1:7" hidden="1">
+    <row r="458" spans="1:7">
       <c r="A458" s="3" t="s">
         <v>61</v>
       </c>
@@ -11291,7 +11305,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="459" spans="1:7" hidden="1">
+    <row r="459" spans="1:7">
       <c r="A459" s="3" t="s">
         <v>61</v>
       </c>
@@ -11314,7 +11328,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="460" spans="1:7" hidden="1">
+    <row r="460" spans="1:7">
       <c r="A460" s="3" t="s">
         <v>61</v>
       </c>
@@ -11337,7 +11351,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="461" spans="1:7" hidden="1">
+    <row r="461" spans="1:7">
       <c r="A461" s="3" t="s">
         <v>61</v>
       </c>
@@ -11360,7 +11374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="462" spans="1:7" hidden="1">
+    <row r="462" spans="1:7">
       <c r="A462" s="3" t="s">
         <v>61</v>
       </c>
@@ -11383,7 +11397,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="463" spans="1:7" hidden="1">
+    <row r="463" spans="1:7">
       <c r="A463" s="3" t="s">
         <v>61</v>
       </c>
@@ -11406,7 +11420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="464" spans="1:7" hidden="1">
+    <row r="464" spans="1:7">
       <c r="A464" s="3" t="s">
         <v>61</v>
       </c>
@@ -11429,7 +11443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="465" spans="1:7" hidden="1">
+    <row r="465" spans="1:7">
       <c r="A465" s="3" t="s">
         <v>61</v>
       </c>
@@ -11452,7 +11466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="466" spans="1:7" hidden="1">
+    <row r="466" spans="1:7">
       <c r="A466" s="3" t="s">
         <v>61</v>
       </c>
@@ -11475,7 +11489,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="467" spans="1:7" hidden="1">
+    <row r="467" spans="1:7">
       <c r="A467" s="3" t="s">
         <v>61</v>
       </c>
@@ -11498,7 +11512,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="468" spans="1:7" hidden="1">
+    <row r="468" spans="1:7">
       <c r="A468" s="3" t="s">
         <v>61</v>
       </c>
@@ -11521,7 +11535,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="469" spans="1:7" hidden="1">
+    <row r="469" spans="1:7">
       <c r="A469" s="3" t="s">
         <v>61</v>
       </c>
@@ -11544,7 +11558,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="470" spans="1:7" hidden="1">
+    <row r="470" spans="1:7">
       <c r="A470" s="3" t="s">
         <v>61</v>
       </c>
@@ -11567,7 +11581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="471" spans="1:7" hidden="1">
+    <row r="471" spans="1:7">
       <c r="A471" s="3" t="s">
         <v>61</v>
       </c>
@@ -11590,7 +11604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="472" spans="1:7" hidden="1">
+    <row r="472" spans="1:7">
       <c r="A472" s="3" t="s">
         <v>61</v>
       </c>
@@ -11613,7 +11627,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="473" spans="1:7" hidden="1">
+    <row r="473" spans="1:7">
       <c r="A473" s="3" t="s">
         <v>61</v>
       </c>
@@ -11636,7 +11650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="474" spans="1:7" hidden="1">
+    <row r="474" spans="1:7">
       <c r="A474" s="3" t="s">
         <v>61</v>
       </c>
@@ -11659,7 +11673,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="475" spans="1:7" hidden="1">
+    <row r="475" spans="1:7">
       <c r="A475" s="3" t="s">
         <v>61</v>
       </c>
@@ -11682,7 +11696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="476" spans="1:7" hidden="1">
+    <row r="476" spans="1:7">
       <c r="A476" s="3" t="s">
         <v>61</v>
       </c>
@@ -11705,7 +11719,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="477" spans="1:7" hidden="1">
+    <row r="477" spans="1:7">
       <c r="A477" s="3" t="s">
         <v>61</v>
       </c>
@@ -11728,7 +11742,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="478" spans="1:7" hidden="1">
+    <row r="478" spans="1:7">
       <c r="A478" s="3" t="s">
         <v>61</v>
       </c>
@@ -11751,7 +11765,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="479" spans="1:7" hidden="1">
+    <row r="479" spans="1:7">
       <c r="A479" s="3" t="s">
         <v>61</v>
       </c>
@@ -11774,7 +11788,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="480" spans="1:7" hidden="1">
+    <row r="480" spans="1:7">
       <c r="A480" s="3" t="s">
         <v>61</v>
       </c>
@@ -11797,7 +11811,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="481" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="481" spans="1:7" s="8" customFormat="1">
       <c r="A481" s="6" t="s">
         <v>61</v>
       </c>
@@ -11820,7 +11834,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="482" spans="1:7" hidden="1">
+    <row r="482" spans="1:7">
       <c r="A482" s="3" t="s">
         <v>61</v>
       </c>
@@ -11843,7 +11857,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="483" spans="1:7" hidden="1">
+    <row r="483" spans="1:7">
       <c r="A483" s="3" t="s">
         <v>61</v>
       </c>
@@ -11866,7 +11880,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="484" spans="1:7" hidden="1">
+    <row r="484" spans="1:7">
       <c r="A484" s="3" t="s">
         <v>61</v>
       </c>
@@ -11889,7 +11903,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="485" spans="1:7" hidden="1">
+    <row r="485" spans="1:7">
       <c r="A485" s="3" t="s">
         <v>61</v>
       </c>
@@ -11912,7 +11926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="486" spans="1:7" hidden="1">
+    <row r="486" spans="1:7">
       <c r="A486" s="3" t="s">
         <v>61</v>
       </c>
@@ -11935,7 +11949,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="487" spans="1:7" hidden="1">
+    <row r="487" spans="1:7">
       <c r="A487" s="3" t="s">
         <v>61</v>
       </c>
@@ -11958,7 +11972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="488" spans="1:7" hidden="1">
+    <row r="488" spans="1:7">
       <c r="A488" s="3" t="s">
         <v>61</v>
       </c>
@@ -11981,7 +11995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="489" spans="1:7" hidden="1">
+    <row r="489" spans="1:7">
       <c r="A489" s="3" t="s">
         <v>61</v>
       </c>
@@ -12004,7 +12018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="490" spans="1:7" hidden="1">
+    <row r="490" spans="1:7">
       <c r="A490" s="3" t="s">
         <v>61</v>
       </c>
@@ -12027,7 +12041,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="491" spans="1:7" hidden="1">
+    <row r="491" spans="1:7">
       <c r="A491" s="3" t="s">
         <v>61</v>
       </c>
@@ -12050,7 +12064,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="492" spans="1:7" hidden="1">
+    <row r="492" spans="1:7">
       <c r="A492" s="3" t="s">
         <v>61</v>
       </c>
@@ -12073,7 +12087,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="493" spans="1:7" hidden="1">
+    <row r="493" spans="1:7">
       <c r="A493" s="3" t="s">
         <v>61</v>
       </c>
@@ -12096,7 +12110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="494" spans="1:7" hidden="1">
+    <row r="494" spans="1:7">
       <c r="A494" s="3" t="s">
         <v>61</v>
       </c>
@@ -12119,7 +12133,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="495" spans="1:7" hidden="1">
+    <row r="495" spans="1:7">
       <c r="A495" s="3" t="s">
         <v>61</v>
       </c>
@@ -12142,7 +12156,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="496" spans="1:7" hidden="1">
+    <row r="496" spans="1:7">
       <c r="A496" s="3" t="s">
         <v>61</v>
       </c>
@@ -12165,7 +12179,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="497" spans="1:7" hidden="1">
+    <row r="497" spans="1:7">
       <c r="A497" s="3" t="s">
         <v>61</v>
       </c>
@@ -12188,7 +12202,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="498" spans="1:7" hidden="1">
+    <row r="498" spans="1:7">
       <c r="A498" s="3" t="s">
         <v>61</v>
       </c>
@@ -12211,7 +12225,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="499" spans="1:7" hidden="1">
+    <row r="499" spans="1:7">
       <c r="A499" s="3" t="s">
         <v>61</v>
       </c>
@@ -12234,7 +12248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="500" spans="1:7" hidden="1">
+    <row r="500" spans="1:7">
       <c r="A500" s="3" t="s">
         <v>61</v>
       </c>
@@ -12257,7 +12271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="501" spans="1:7" hidden="1">
+    <row r="501" spans="1:7">
       <c r="A501" s="3" t="s">
         <v>61</v>
       </c>
@@ -12280,7 +12294,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="502" spans="1:7" hidden="1">
+    <row r="502" spans="1:7">
       <c r="A502" s="3" t="s">
         <v>61</v>
       </c>
@@ -12303,7 +12317,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="503" spans="1:7" hidden="1">
+    <row r="503" spans="1:7">
       <c r="A503" s="3" t="s">
         <v>61</v>
       </c>
@@ -12326,7 +12340,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="504" spans="1:7" hidden="1">
+    <row r="504" spans="1:7">
       <c r="A504" s="3" t="s">
         <v>61</v>
       </c>
@@ -12349,7 +12363,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="505" spans="1:7" hidden="1">
+    <row r="505" spans="1:7">
       <c r="A505" s="3" t="s">
         <v>61</v>
       </c>
@@ -12372,7 +12386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="506" spans="1:7" hidden="1">
+    <row r="506" spans="1:7">
       <c r="A506" s="3" t="s">
         <v>61</v>
       </c>
@@ -12395,7 +12409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="507" spans="1:7" hidden="1">
+    <row r="507" spans="1:7">
       <c r="A507" s="3" t="s">
         <v>61</v>
       </c>
@@ -12418,7 +12432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="508" spans="1:7" hidden="1">
+    <row r="508" spans="1:7">
       <c r="A508" s="3" t="s">
         <v>61</v>
       </c>
@@ -12441,7 +12455,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="509" spans="1:7" hidden="1">
+    <row r="509" spans="1:7">
       <c r="A509" s="3" t="s">
         <v>61</v>
       </c>
@@ -12464,7 +12478,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="510" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="510" spans="1:7" s="8" customFormat="1">
       <c r="A510" s="6" t="s">
         <v>61</v>
       </c>
@@ -12487,7 +12501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="511" spans="1:7" hidden="1">
+    <row r="511" spans="1:7">
       <c r="A511" s="3" t="s">
         <v>61</v>
       </c>
@@ -12510,7 +12524,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="512" spans="1:7" hidden="1">
+    <row r="512" spans="1:7">
       <c r="A512" s="3" t="s">
         <v>61</v>
       </c>
@@ -12533,7 +12547,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="513" spans="1:7" hidden="1">
+    <row r="513" spans="1:7">
       <c r="A513" s="3" t="s">
         <v>61</v>
       </c>
@@ -12556,7 +12570,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="514" spans="1:7" hidden="1">
+    <row r="514" spans="1:7">
       <c r="A514" s="3" t="s">
         <v>61</v>
       </c>
@@ -12579,7 +12593,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="515" spans="1:7" hidden="1">
+    <row r="515" spans="1:7">
       <c r="A515" s="3" t="s">
         <v>61</v>
       </c>
@@ -12602,7 +12616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="516" spans="1:7" hidden="1">
+    <row r="516" spans="1:7">
       <c r="A516" s="3" t="s">
         <v>61</v>
       </c>
@@ -12625,7 +12639,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="517" spans="1:7" hidden="1">
+    <row r="517" spans="1:7">
       <c r="A517" s="3" t="s">
         <v>61</v>
       </c>
@@ -12648,7 +12662,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="518" spans="1:7" hidden="1">
+    <row r="518" spans="1:7">
       <c r="A518" s="3" t="s">
         <v>61</v>
       </c>
@@ -12671,7 +12685,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="519" spans="1:7" hidden="1">
+    <row r="519" spans="1:7">
       <c r="A519" s="3" t="s">
         <v>61</v>
       </c>
@@ -12694,7 +12708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="520" spans="1:7" hidden="1">
+    <row r="520" spans="1:7">
       <c r="A520" s="3" t="s">
         <v>61</v>
       </c>
@@ -12717,7 +12731,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="521" spans="1:7" hidden="1">
+    <row r="521" spans="1:7">
       <c r="A521" s="3" t="s">
         <v>61</v>
       </c>
@@ -12740,7 +12754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="522" spans="1:7" hidden="1">
+    <row r="522" spans="1:7">
       <c r="A522" s="3" t="s">
         <v>61</v>
       </c>
@@ -12763,7 +12777,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="523" spans="1:7" hidden="1">
+    <row r="523" spans="1:7">
       <c r="A523" s="3" t="s">
         <v>61</v>
       </c>
@@ -12786,7 +12800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="524" spans="1:7" hidden="1">
+    <row r="524" spans="1:7">
       <c r="A524" s="3" t="s">
         <v>61</v>
       </c>
@@ -12809,7 +12823,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="525" spans="1:7" hidden="1">
+    <row r="525" spans="1:7">
       <c r="A525" s="3" t="s">
         <v>61</v>
       </c>
@@ -12832,7 +12846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="526" spans="1:7" hidden="1">
+    <row r="526" spans="1:7">
       <c r="A526" s="3" t="s">
         <v>61</v>
       </c>
@@ -12855,7 +12869,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="527" spans="1:7" hidden="1">
+    <row r="527" spans="1:7">
       <c r="A527" s="3" t="s">
         <v>61</v>
       </c>
@@ -12878,7 +12892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="528" spans="1:7" hidden="1">
+    <row r="528" spans="1:7">
       <c r="A528" s="3" t="s">
         <v>61</v>
       </c>
@@ -12901,7 +12915,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="529" spans="1:7" hidden="1">
+    <row r="529" spans="1:7">
       <c r="A529" s="3" t="s">
         <v>61</v>
       </c>
@@ -12924,7 +12938,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="530" spans="1:7" hidden="1">
+    <row r="530" spans="1:7">
       <c r="A530" s="3" t="s">
         <v>61</v>
       </c>
@@ -12947,7 +12961,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="531" spans="1:7" hidden="1">
+    <row r="531" spans="1:7">
       <c r="A531" s="3" t="s">
         <v>61</v>
       </c>
@@ -12970,7 +12984,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="532" spans="1:7" hidden="1">
+    <row r="532" spans="1:7">
       <c r="A532" s="3" t="s">
         <v>61</v>
       </c>
@@ -12993,7 +13007,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="533" spans="1:7" hidden="1">
+    <row r="533" spans="1:7">
       <c r="A533" s="3" t="s">
         <v>61</v>
       </c>
@@ -13016,7 +13030,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="534" spans="1:7" hidden="1">
+    <row r="534" spans="1:7">
       <c r="A534" s="3" t="s">
         <v>61</v>
       </c>
@@ -13039,7 +13053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="535" spans="1:7" hidden="1">
+    <row r="535" spans="1:7">
       <c r="A535" s="3" t="s">
         <v>61</v>
       </c>
@@ -13062,7 +13076,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="536" spans="1:7" hidden="1">
+    <row r="536" spans="1:7">
       <c r="A536" s="3" t="s">
         <v>61</v>
       </c>
@@ -13085,7 +13099,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="537" spans="1:7" hidden="1">
+    <row r="537" spans="1:7">
       <c r="A537" s="3" t="s">
         <v>61</v>
       </c>
@@ -13108,7 +13122,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="538" spans="1:7" hidden="1">
+    <row r="538" spans="1:7">
       <c r="A538" s="3" t="s">
         <v>61</v>
       </c>
@@ -13131,7 +13145,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="539" spans="1:7" s="8" customFormat="1" hidden="1">
+    <row r="539" spans="1:7" s="8" customFormat="1">
       <c r="A539" s="6" t="s">
         <v>83</v>
       </c>
@@ -13154,7 +13168,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="540" spans="1:7" hidden="1">
+    <row r="540" spans="1:7">
       <c r="A540" s="3" t="s">
         <v>83</v>
       </c>
@@ -13177,7 +13191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="541" spans="1:7" hidden="1">
+    <row r="541" spans="1:7">
       <c r="A541" s="3" t="s">
         <v>83</v>
       </c>
@@ -13200,7 +13214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="542" spans="1:7" hidden="1">
+    <row r="542" spans="1:7">
       <c r="A542" s="3" t="s">
         <v>83</v>
       </c>
@@ -13223,7 +13237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="543" spans="1:7" hidden="1">
+    <row r="543" spans="1:7">
       <c r="A543" s="3" t="s">
         <v>83</v>
       </c>
@@ -13246,7 +13260,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="544" spans="1:7" hidden="1">
+    <row r="544" spans="1:7">
       <c r="A544" s="3" t="s">
         <v>83</v>
       </c>
@@ -13269,7 +13283,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="545" spans="1:7" hidden="1">
+    <row r="545" spans="1:7">
       <c r="A545" s="3" t="s">
         <v>83</v>
       </c>
@@ -13292,7 +13306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="546" spans="1:7" hidden="1">
+    <row r="546" spans="1:7">
       <c r="A546" s="3" t="s">
         <v>83</v>
       </c>
@@ -13315,7 +13329,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="547" spans="1:7" hidden="1">
+    <row r="547" spans="1:7">
       <c r="A547" s="3" t="s">
         <v>83</v>
       </c>
@@ -13338,7 +13352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="548" spans="1:7" hidden="1">
+    <row r="548" spans="1:7">
       <c r="A548" s="3" t="s">
         <v>83</v>
       </c>
@@ -13361,7 +13375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="549" spans="1:7" hidden="1">
+    <row r="549" spans="1:7">
       <c r="A549" s="3" t="s">
         <v>83</v>
       </c>
@@ -13384,7 +13398,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="550" spans="1:7" hidden="1">
+    <row r="550" spans="1:7">
       <c r="A550" s="3" t="s">
         <v>83</v>
       </c>
@@ -13407,7 +13421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="551" spans="1:7" hidden="1">
+    <row r="551" spans="1:7">
       <c r="A551" s="3" t="s">
         <v>83</v>
       </c>
@@ -13430,7 +13444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="552" spans="1:7" hidden="1">
+    <row r="552" spans="1:7">
       <c r="A552" s="3" t="s">
         <v>83</v>
       </c>
@@ -13453,7 +13467,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="553" spans="1:7" hidden="1">
+    <row r="553" spans="1:7">
       <c r="A553" s="3" t="s">
         <v>83</v>
       </c>
@@ -13476,7 +13490,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="554" spans="1:7" hidden="1">
+    <row r="554" spans="1:7">
       <c r="A554" s="3" t="s">
         <v>83</v>
       </c>
@@ -13499,7 +13513,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="555" spans="1:7" hidden="1">
+    <row r="555" spans="1:7">
       <c r="A555" s="3" t="s">
         <v>83</v>
       </c>
@@ -13522,7 +13536,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="556" spans="1:7" hidden="1">
+    <row r="556" spans="1:7">
       <c r="A556" s="3" t="s">
         <v>83</v>
       </c>
@@ -13545,7 +13559,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="557" spans="1:7" hidden="1">
+    <row r="557" spans="1:7">
       <c r="A557" s="3" t="s">
         <v>83</v>
       </c>
@@ -13568,7 +13582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="558" spans="1:7" hidden="1">
+    <row r="558" spans="1:7">
       <c r="A558" s="3" t="s">
         <v>83</v>
       </c>
@@ -13591,7 +13605,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="559" spans="1:7" hidden="1">
+    <row r="559" spans="1:7">
       <c r="A559" s="3" t="s">
         <v>83</v>
       </c>
@@ -13614,7 +13628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="560" spans="1:7" hidden="1">
+    <row r="560" spans="1:7">
       <c r="A560" s="3" t="s">
         <v>83</v>
       </c>
@@ -13637,7 +13651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="561" spans="1:7" hidden="1">
+    <row r="561" spans="1:7">
       <c r="A561" s="3" t="s">
         <v>83</v>
       </c>
@@ -13660,7 +13674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="562" spans="1:7" hidden="1">
+    <row r="562" spans="1:7">
       <c r="A562" s="3" t="s">
         <v>83</v>
       </c>
@@ -13683,7 +13697,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="563" spans="1:7" hidden="1">
+    <row r="563" spans="1:7">
       <c r="A563" s="3" t="s">
         <v>83</v>
       </c>
@@ -13706,7 +13720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="564" spans="1:7" hidden="1">
+    <row r="564" spans="1:7">
       <c r="A564" s="3" t="s">
         <v>83</v>
       </c>
@@ -13729,7 +13743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="565" spans="1:7" hidden="1">
+    <row r="565" spans="1:7">
       <c r="A565" s="3" t="s">
         <v>83</v>
       </c>
@@ -13752,7 +13766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="566" spans="1:7" hidden="1">
+    <row r="566" spans="1:7">
       <c r="A566" s="3" t="s">
         <v>83</v>
       </c>
@@ -13775,7 +13789,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="567" spans="1:7" hidden="1">
+    <row r="567" spans="1:7">
       <c r="A567" s="3" t="s">
         <v>83</v>
       </c>
@@ -13798,7 +13812,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="568" spans="1:7" hidden="1">
+    <row r="568" spans="1:7">
       <c r="A568" s="3" t="s">
         <v>83</v>
       </c>
@@ -13821,7 +13835,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="569" spans="1:7" hidden="1">
+    <row r="569" spans="1:7">
       <c r="A569" s="3" t="s">
         <v>83</v>
       </c>
@@ -13844,7 +13858,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="570" spans="1:7" hidden="1">
+    <row r="570" spans="1:7">
       <c r="A570" s="3" t="s">
         <v>83</v>
       </c>
@@ -13867,7 +13881,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="571" spans="1:7" hidden="1">
+    <row r="571" spans="1:7">
       <c r="A571" s="3" t="s">
         <v>83</v>
       </c>
@@ -13890,7 +13904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="572" spans="1:7" hidden="1">
+    <row r="572" spans="1:7">
       <c r="A572" s="3" t="s">
         <v>83</v>
       </c>
@@ -13913,7 +13927,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="573" spans="1:7" hidden="1">
+    <row r="573" spans="1:7">
       <c r="A573" s="3" t="s">
         <v>83</v>
       </c>
@@ -13936,7 +13950,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="574" spans="1:7" hidden="1">
+    <row r="574" spans="1:7">
       <c r="A574" s="3" t="s">
         <v>83</v>
       </c>
@@ -13959,7 +13973,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="575" spans="1:7" hidden="1">
+    <row r="575" spans="1:7">
       <c r="A575" s="3" t="s">
         <v>83</v>
       </c>
@@ -13982,7 +13996,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="576" spans="1:7" hidden="1">
+    <row r="576" spans="1:7">
       <c r="A576" s="3" t="s">
         <v>83</v>
       </c>
@@ -14005,7 +14019,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="577" spans="1:7" hidden="1">
+    <row r="577" spans="1:7">
       <c r="A577" s="3" t="s">
         <v>83</v>
       </c>
@@ -14028,7 +14042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="578" spans="1:7" hidden="1">
+    <row r="578" spans="1:7">
       <c r="A578" s="3" t="s">
         <v>83</v>
       </c>
@@ -14051,7 +14065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="579" spans="1:7" hidden="1">
+    <row r="579" spans="1:7">
       <c r="A579" s="6" t="s">
         <v>86</v>
       </c>
@@ -14074,7 +14088,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="580" spans="1:7" hidden="1">
+    <row r="580" spans="1:7">
       <c r="A580" s="3" t="s">
         <v>86</v>
       </c>
@@ -14097,7 +14111,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="581" spans="1:7" hidden="1">
+    <row r="581" spans="1:7">
       <c r="A581" s="3" t="s">
         <v>86</v>
       </c>
@@ -14120,7 +14134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="582" spans="1:7" hidden="1">
+    <row r="582" spans="1:7">
       <c r="A582" s="3" t="s">
         <v>86</v>
       </c>
@@ -14143,7 +14157,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="583" spans="1:7" hidden="1">
+    <row r="583" spans="1:7">
       <c r="A583" s="3" t="s">
         <v>86</v>
       </c>
@@ -14166,7 +14180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="584" spans="1:7" hidden="1">
+    <row r="584" spans="1:7">
       <c r="A584" s="3" t="s">
         <v>86</v>
       </c>
@@ -14189,7 +14203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="585" spans="1:7" hidden="1">
+    <row r="585" spans="1:7">
       <c r="A585" s="3" t="s">
         <v>86</v>
       </c>
@@ -14212,7 +14226,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="586" spans="1:7" hidden="1">
+    <row r="586" spans="1:7">
       <c r="A586" s="3" t="s">
         <v>86</v>
       </c>
@@ -14235,7 +14249,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="587" spans="1:7" hidden="1">
+    <row r="587" spans="1:7">
       <c r="A587" s="3" t="s">
         <v>86</v>
       </c>
@@ -14258,7 +14272,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="588" spans="1:7" hidden="1">
+    <row r="588" spans="1:7">
       <c r="A588" s="3" t="s">
         <v>86</v>
       </c>
@@ -14281,7 +14295,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="589" spans="1:7" hidden="1">
+    <row r="589" spans="1:7">
       <c r="A589" s="3" t="s">
         <v>86</v>
       </c>
@@ -14304,7 +14318,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="590" spans="1:7" hidden="1">
+    <row r="590" spans="1:7">
       <c r="A590" s="3" t="s">
         <v>86</v>
       </c>
@@ -14327,7 +14341,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="591" spans="1:7" hidden="1">
+    <row r="591" spans="1:7">
       <c r="A591" s="3" t="s">
         <v>86</v>
       </c>
@@ -14350,7 +14364,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="592" spans="1:7" hidden="1">
+    <row r="592" spans="1:7">
       <c r="A592" s="3" t="s">
         <v>86</v>
       </c>
@@ -14373,7 +14387,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="593" spans="1:7" hidden="1">
+    <row r="593" spans="1:7">
       <c r="A593" s="3" t="s">
         <v>86</v>
       </c>
@@ -14396,7 +14410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="594" spans="1:7" hidden="1">
+    <row r="594" spans="1:7">
       <c r="A594" s="3" t="s">
         <v>86</v>
       </c>
@@ -14419,7 +14433,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="595" spans="1:7" hidden="1">
+    <row r="595" spans="1:7">
       <c r="A595" s="3" t="s">
         <v>86</v>
       </c>
@@ -14442,7 +14456,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="596" spans="1:7" hidden="1">
+    <row r="596" spans="1:7">
       <c r="A596" s="3" t="s">
         <v>86</v>
       </c>
@@ -14465,7 +14479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="597" spans="1:7" hidden="1">
+    <row r="597" spans="1:7">
       <c r="A597" s="3" t="s">
         <v>86</v>
       </c>
@@ -14488,7 +14502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="598" spans="1:7" hidden="1">
+    <row r="598" spans="1:7">
       <c r="A598" s="3" t="s">
         <v>86</v>
       </c>
@@ -14511,7 +14525,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="599" spans="1:7" hidden="1">
+    <row r="599" spans="1:7">
       <c r="A599" s="3" t="s">
         <v>86</v>
       </c>
@@ -14534,7 +14548,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="600" spans="1:7" hidden="1">
+    <row r="600" spans="1:7">
       <c r="A600" s="3" t="s">
         <v>86</v>
       </c>
@@ -14557,7 +14571,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="601" spans="1:7" hidden="1">
+    <row r="601" spans="1:7">
       <c r="A601" s="3" t="s">
         <v>86</v>
       </c>
@@ -14580,7 +14594,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="602" spans="1:7" hidden="1">
+    <row r="602" spans="1:7">
       <c r="A602" s="3" t="s">
         <v>86</v>
       </c>
@@ -14603,7 +14617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="603" spans="1:7" hidden="1">
+    <row r="603" spans="1:7">
       <c r="A603" s="3" t="s">
         <v>86</v>
       </c>
@@ -14626,7 +14640,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="604" spans="1:7" hidden="1">
+    <row r="604" spans="1:7">
       <c r="A604" s="3" t="s">
         <v>86</v>
       </c>
@@ -14649,7 +14663,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="605" spans="1:7" hidden="1">
+    <row r="605" spans="1:7">
       <c r="A605" s="3" t="s">
         <v>86</v>
       </c>
@@ -14672,7 +14686,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="606" spans="1:7" hidden="1">
+    <row r="606" spans="1:7">
       <c r="A606" s="3" t="s">
         <v>86</v>
       </c>
@@ -14695,7 +14709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="607" spans="1:7" hidden="1">
+    <row r="607" spans="1:7">
       <c r="A607" s="3" t="s">
         <v>86</v>
       </c>
@@ -14718,7 +14732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="608" spans="1:7" hidden="1">
+    <row r="608" spans="1:7">
       <c r="A608" s="6" t="s">
         <v>86</v>
       </c>
@@ -14741,7 +14755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="609" spans="1:7" hidden="1">
+    <row r="609" spans="1:7">
       <c r="A609" s="3" t="s">
         <v>86</v>
       </c>
@@ -14764,7 +14778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="610" spans="1:7" hidden="1">
+    <row r="610" spans="1:7">
       <c r="A610" s="3" t="s">
         <v>86</v>
       </c>
@@ -14787,7 +14801,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="611" spans="1:7" hidden="1">
+    <row r="611" spans="1:7">
       <c r="A611" s="3" t="s">
         <v>86</v>
       </c>
@@ -14810,7 +14824,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="612" spans="1:7" hidden="1">
+    <row r="612" spans="1:7">
       <c r="A612" s="3" t="s">
         <v>86</v>
       </c>
@@ -14833,7 +14847,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="613" spans="1:7" hidden="1">
+    <row r="613" spans="1:7">
       <c r="A613" s="3" t="s">
         <v>86</v>
       </c>
@@ -14856,7 +14870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="614" spans="1:7" hidden="1">
+    <row r="614" spans="1:7">
       <c r="A614" s="3" t="s">
         <v>86</v>
       </c>
@@ -14879,7 +14893,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="615" spans="1:7" hidden="1">
+    <row r="615" spans="1:7">
       <c r="A615" s="3" t="s">
         <v>86</v>
       </c>
@@ -14902,7 +14916,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="616" spans="1:7" hidden="1">
+    <row r="616" spans="1:7">
       <c r="A616" s="3" t="s">
         <v>86</v>
       </c>
@@ -14925,7 +14939,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="617" spans="1:7" hidden="1">
+    <row r="617" spans="1:7">
       <c r="A617" s="3" t="s">
         <v>86</v>
       </c>
@@ -14948,7 +14962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="618" spans="1:7" hidden="1">
+    <row r="618" spans="1:7">
       <c r="A618" s="3" t="s">
         <v>86</v>
       </c>
@@ -14971,7 +14985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="619" spans="1:7" hidden="1">
+    <row r="619" spans="1:7">
       <c r="A619" s="3" t="s">
         <v>86</v>
       </c>
@@ -14994,7 +15008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="620" spans="1:7" hidden="1">
+    <row r="620" spans="1:7">
       <c r="A620" s="3" t="s">
         <v>86</v>
       </c>
@@ -15017,7 +15031,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="621" spans="1:7" hidden="1">
+    <row r="621" spans="1:7">
       <c r="A621" s="3" t="s">
         <v>86</v>
       </c>
@@ -15040,7 +15054,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="622" spans="1:7" hidden="1">
+    <row r="622" spans="1:7">
       <c r="A622" s="3" t="s">
         <v>86</v>
       </c>
@@ -15063,7 +15077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="623" spans="1:7" hidden="1">
+    <row r="623" spans="1:7">
       <c r="A623" s="3" t="s">
         <v>86</v>
       </c>
@@ -15086,7 +15100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="624" spans="1:7" hidden="1">
+    <row r="624" spans="1:7">
       <c r="A624" s="3" t="s">
         <v>86</v>
       </c>
@@ -15109,7 +15123,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="625" spans="1:7" hidden="1">
+    <row r="625" spans="1:7">
       <c r="A625" s="3" t="s">
         <v>86</v>
       </c>
@@ -15132,7 +15146,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="626" spans="1:7" hidden="1">
+    <row r="626" spans="1:7">
       <c r="A626" s="3" t="s">
         <v>86</v>
       </c>
@@ -15155,7 +15169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="627" spans="1:7" hidden="1">
+    <row r="627" spans="1:7">
       <c r="A627" s="3" t="s">
         <v>86</v>
       </c>
@@ -15178,7 +15192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="628" spans="1:7" hidden="1">
+    <row r="628" spans="1:7">
       <c r="A628" s="3" t="s">
         <v>86</v>
       </c>
@@ -15201,7 +15215,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="629" spans="1:7" hidden="1">
+    <row r="629" spans="1:7">
       <c r="A629" s="3" t="s">
         <v>86</v>
       </c>
@@ -15224,7 +15238,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="630" spans="1:7" hidden="1">
+    <row r="630" spans="1:7">
       <c r="A630" s="3" t="s">
         <v>86</v>
       </c>
@@ -15247,7 +15261,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="631" spans="1:7" hidden="1">
+    <row r="631" spans="1:7">
       <c r="A631" s="3" t="s">
         <v>86</v>
       </c>
@@ -15270,7 +15284,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="632" spans="1:7" hidden="1">
+    <row r="632" spans="1:7">
       <c r="A632" s="3" t="s">
         <v>86</v>
       </c>
@@ -15293,7 +15307,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="633" spans="1:7" hidden="1">
+    <row r="633" spans="1:7">
       <c r="A633" s="3" t="s">
         <v>86</v>
       </c>
@@ -15316,7 +15330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="634" spans="1:7" hidden="1">
+    <row r="634" spans="1:7">
       <c r="A634" s="3" t="s">
         <v>86</v>
       </c>
@@ -15339,7 +15353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="635" spans="1:7" hidden="1">
+    <row r="635" spans="1:7">
       <c r="A635" s="3" t="s">
         <v>86</v>
       </c>
@@ -15362,7 +15376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="636" spans="1:7" hidden="1">
+    <row r="636" spans="1:7">
       <c r="A636" s="3" t="s">
         <v>86</v>
       </c>
@@ -15385,7 +15399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="637" spans="1:7" hidden="1">
+    <row r="637" spans="1:7">
       <c r="A637" s="6" t="s">
         <v>86</v>
       </c>
@@ -15408,7 +15422,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="638" spans="1:7" hidden="1">
+    <row r="638" spans="1:7">
       <c r="A638" s="3" t="s">
         <v>86</v>
       </c>
@@ -15431,7 +15445,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="639" spans="1:7" hidden="1">
+    <row r="639" spans="1:7">
       <c r="A639" s="3" t="s">
         <v>86</v>
       </c>
@@ -15454,7 +15468,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="640" spans="1:7" hidden="1">
+    <row r="640" spans="1:7">
       <c r="A640" s="3" t="s">
         <v>86</v>
       </c>
@@ -15477,7 +15491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="641" spans="1:7" hidden="1">
+    <row r="641" spans="1:7">
       <c r="A641" s="3" t="s">
         <v>86</v>
       </c>
@@ -15500,7 +15514,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="642" spans="1:7" hidden="1">
+    <row r="642" spans="1:7">
       <c r="A642" s="3" t="s">
         <v>86</v>
       </c>
@@ -15523,7 +15537,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="643" spans="1:7" hidden="1">
+    <row r="643" spans="1:7">
       <c r="A643" s="3" t="s">
         <v>86</v>
       </c>
@@ -15546,7 +15560,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="644" spans="1:7" hidden="1">
+    <row r="644" spans="1:7">
       <c r="A644" s="3" t="s">
         <v>86</v>
       </c>
@@ -15569,7 +15583,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="645" spans="1:7" hidden="1">
+    <row r="645" spans="1:7">
       <c r="A645" s="3" t="s">
         <v>86</v>
       </c>
@@ -15592,7 +15606,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="646" spans="1:7" hidden="1">
+    <row r="646" spans="1:7">
       <c r="A646" s="3" t="s">
         <v>86</v>
       </c>
@@ -15615,7 +15629,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="647" spans="1:7" hidden="1">
+    <row r="647" spans="1:7">
       <c r="A647" s="3" t="s">
         <v>86</v>
       </c>
@@ -15638,7 +15652,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="648" spans="1:7" hidden="1">
+    <row r="648" spans="1:7">
       <c r="A648" s="3" t="s">
         <v>86</v>
       </c>
@@ -15661,7 +15675,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="649" spans="1:7" hidden="1">
+    <row r="649" spans="1:7">
       <c r="A649" s="3" t="s">
         <v>86</v>
       </c>
@@ -15684,7 +15698,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="650" spans="1:7" hidden="1">
+    <row r="650" spans="1:7">
       <c r="A650" s="3" t="s">
         <v>86</v>
       </c>
@@ -15707,7 +15721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="651" spans="1:7" hidden="1">
+    <row r="651" spans="1:7">
       <c r="A651" s="3" t="s">
         <v>86</v>
       </c>
@@ -15730,7 +15744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="652" spans="1:7" hidden="1">
+    <row r="652" spans="1:7">
       <c r="A652" s="3" t="s">
         <v>86</v>
       </c>
@@ -15753,7 +15767,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="653" spans="1:7" hidden="1">
+    <row r="653" spans="1:7">
       <c r="A653" s="3" t="s">
         <v>86</v>
       </c>
@@ -15776,7 +15790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="654" spans="1:7" hidden="1">
+    <row r="654" spans="1:7">
       <c r="A654" s="3" t="s">
         <v>86</v>
       </c>
@@ -15799,7 +15813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="655" spans="1:7" hidden="1">
+    <row r="655" spans="1:7">
       <c r="A655" s="3" t="s">
         <v>86</v>
       </c>
@@ -15822,7 +15836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="656" spans="1:7" hidden="1">
+    <row r="656" spans="1:7">
       <c r="A656" s="3" t="s">
         <v>86</v>
       </c>
@@ -15845,7 +15859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="657" spans="1:7" hidden="1">
+    <row r="657" spans="1:7">
       <c r="A657" s="3" t="s">
         <v>86</v>
       </c>
@@ -15868,7 +15882,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="658" spans="1:7" hidden="1">
+    <row r="658" spans="1:7">
       <c r="A658" s="3" t="s">
         <v>86</v>
       </c>
@@ -15891,7 +15905,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="659" spans="1:7" hidden="1">
+    <row r="659" spans="1:7">
       <c r="A659" s="3" t="s">
         <v>86</v>
       </c>
@@ -15914,7 +15928,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="660" spans="1:7" hidden="1">
+    <row r="660" spans="1:7">
       <c r="A660" s="3" t="s">
         <v>86</v>
       </c>
@@ -15937,7 +15951,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="661" spans="1:7" hidden="1">
+    <row r="661" spans="1:7">
       <c r="A661" s="3" t="s">
         <v>86</v>
       </c>
@@ -15960,7 +15974,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="662" spans="1:7" hidden="1">
+    <row r="662" spans="1:7">
       <c r="A662" s="3" t="s">
         <v>86</v>
       </c>
@@ -15983,7 +15997,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="663" spans="1:7" hidden="1">
+    <row r="663" spans="1:7">
       <c r="A663" s="3" t="s">
         <v>86</v>
       </c>
@@ -16006,7 +16020,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="664" spans="1:7" hidden="1">
+    <row r="664" spans="1:7">
       <c r="A664" s="3" t="s">
         <v>86</v>
       </c>
@@ -16029,7 +16043,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="665" spans="1:7" hidden="1">
+    <row r="665" spans="1:7">
       <c r="A665" s="3" t="s">
         <v>86</v>
       </c>
@@ -16052,7 +16066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="666" spans="1:7" hidden="1">
+    <row r="666" spans="1:7">
       <c r="A666" s="6" t="s">
         <v>87</v>
       </c>
@@ -16075,7 +16089,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="667" spans="1:7" hidden="1">
+    <row r="667" spans="1:7">
       <c r="A667" s="3" t="s">
         <v>87</v>
       </c>
@@ -16098,7 +16112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="668" spans="1:7" hidden="1">
+    <row r="668" spans="1:7">
       <c r="A668" s="3" t="s">
         <v>87</v>
       </c>
@@ -16121,7 +16135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="669" spans="1:7" hidden="1">
+    <row r="669" spans="1:7">
       <c r="A669" s="3" t="s">
         <v>87</v>
       </c>
@@ -16144,7 +16158,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="670" spans="1:7" hidden="1">
+    <row r="670" spans="1:7">
       <c r="A670" s="3" t="s">
         <v>87</v>
       </c>
@@ -16167,7 +16181,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="671" spans="1:7" hidden="1">
+    <row r="671" spans="1:7">
       <c r="A671" s="3" t="s">
         <v>87</v>
       </c>
@@ -16190,7 +16204,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="672" spans="1:7" hidden="1">
+    <row r="672" spans="1:7">
       <c r="A672" s="3" t="s">
         <v>87</v>
       </c>
@@ -16213,7 +16227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="673" spans="1:7" hidden="1">
+    <row r="673" spans="1:7">
       <c r="A673" s="3" t="s">
         <v>87</v>
       </c>
@@ -16236,7 +16250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="674" spans="1:7" hidden="1">
+    <row r="674" spans="1:7">
       <c r="A674" s="3" t="s">
         <v>87</v>
       </c>
@@ -16259,7 +16273,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="675" spans="1:7" hidden="1">
+    <row r="675" spans="1:7">
       <c r="A675" s="3" t="s">
         <v>87</v>
       </c>
@@ -16282,7 +16296,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="676" spans="1:7" hidden="1">
+    <row r="676" spans="1:7">
       <c r="A676" s="3" t="s">
         <v>87</v>
       </c>
@@ -16305,7 +16319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="677" spans="1:7" hidden="1">
+    <row r="677" spans="1:7">
       <c r="A677" s="3" t="s">
         <v>87</v>
       </c>
@@ -16328,7 +16342,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="678" spans="1:7" hidden="1">
+    <row r="678" spans="1:7">
       <c r="A678" s="3" t="s">
         <v>87</v>
       </c>
@@ -16351,7 +16365,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="679" spans="1:7" hidden="1">
+    <row r="679" spans="1:7">
       <c r="A679" s="3" t="s">
         <v>87</v>
       </c>
@@ -16374,7 +16388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="680" spans="1:7" hidden="1">
+    <row r="680" spans="1:7">
       <c r="A680" s="3" t="s">
         <v>87</v>
       </c>
@@ -16397,7 +16411,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="681" spans="1:7" hidden="1">
+    <row r="681" spans="1:7">
       <c r="A681" s="3" t="s">
         <v>87</v>
       </c>
@@ -16420,7 +16434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="682" spans="1:7" hidden="1">
+    <row r="682" spans="1:7">
       <c r="A682" s="3" t="s">
         <v>87</v>
       </c>
@@ -16443,7 +16457,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="683" spans="1:7" hidden="1">
+    <row r="683" spans="1:7">
       <c r="A683" s="3" t="s">
         <v>87</v>
       </c>
@@ -16466,7 +16480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="684" spans="1:7" hidden="1">
+    <row r="684" spans="1:7">
       <c r="A684" s="3" t="s">
         <v>87</v>
       </c>
@@ -16489,7 +16503,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="685" spans="1:7" hidden="1">
+    <row r="685" spans="1:7">
       <c r="A685" s="3" t="s">
         <v>87</v>
       </c>
@@ -16512,7 +16526,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="686" spans="1:7" hidden="1">
+    <row r="686" spans="1:7">
       <c r="A686" s="3" t="s">
         <v>87</v>
       </c>
@@ -16535,7 +16549,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="687" spans="1:7" hidden="1">
+    <row r="687" spans="1:7">
       <c r="A687" s="3" t="s">
         <v>87</v>
       </c>
@@ -16558,7 +16572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="688" spans="1:7" hidden="1">
+    <row r="688" spans="1:7">
       <c r="A688" s="3" t="s">
         <v>87</v>
       </c>
@@ -16581,7 +16595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="689" spans="1:7" hidden="1">
+    <row r="689" spans="1:7">
       <c r="A689" s="3" t="s">
         <v>87</v>
       </c>
@@ -16604,7 +16618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="690" spans="1:7" hidden="1">
+    <row r="690" spans="1:7">
       <c r="A690" s="3" t="s">
         <v>87</v>
       </c>
@@ -16627,7 +16641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="691" spans="1:7" hidden="1">
+    <row r="691" spans="1:7">
       <c r="A691" s="3" t="s">
         <v>87</v>
       </c>
@@ -16650,7 +16664,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="692" spans="1:7" hidden="1">
+    <row r="692" spans="1:7">
       <c r="A692" s="3" t="s">
         <v>87</v>
       </c>
@@ -16673,7 +16687,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="693" spans="1:7" hidden="1">
+    <row r="693" spans="1:7">
       <c r="A693" s="3" t="s">
         <v>87</v>
       </c>
@@ -16696,7 +16710,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="694" spans="1:7" hidden="1">
+    <row r="694" spans="1:7">
       <c r="A694" s="3" t="s">
         <v>87</v>
       </c>
@@ -16719,7 +16733,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="695" spans="1:7" hidden="1">
+    <row r="695" spans="1:7">
       <c r="A695" s="6" t="s">
         <v>87</v>
       </c>
@@ -16742,7 +16756,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="696" spans="1:7" hidden="1">
+    <row r="696" spans="1:7">
       <c r="A696" s="3" t="s">
         <v>87</v>
       </c>
@@ -16765,7 +16779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="697" spans="1:7" hidden="1">
+    <row r="697" spans="1:7">
       <c r="A697" s="3" t="s">
         <v>87</v>
       </c>
@@ -16788,7 +16802,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="698" spans="1:7" hidden="1">
+    <row r="698" spans="1:7">
       <c r="A698" s="3" t="s">
         <v>87</v>
       </c>
@@ -16811,7 +16825,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="699" spans="1:7" hidden="1">
+    <row r="699" spans="1:7">
       <c r="A699" s="3" t="s">
         <v>87</v>
       </c>
@@ -16834,7 +16848,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="700" spans="1:7" hidden="1">
+    <row r="700" spans="1:7">
       <c r="A700" s="3" t="s">
         <v>87</v>
       </c>
@@ -16857,7 +16871,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="701" spans="1:7" hidden="1">
+    <row r="701" spans="1:7">
       <c r="A701" s="3" t="s">
         <v>87</v>
       </c>
@@ -16880,7 +16894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="702" spans="1:7" hidden="1">
+    <row r="702" spans="1:7">
       <c r="A702" s="3" t="s">
         <v>87</v>
       </c>
@@ -16903,7 +16917,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="703" spans="1:7" hidden="1">
+    <row r="703" spans="1:7">
       <c r="A703" s="3" t="s">
         <v>87</v>
       </c>
@@ -16926,7 +16940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="704" spans="1:7" hidden="1">
+    <row r="704" spans="1:7">
       <c r="A704" s="3" t="s">
         <v>87</v>
       </c>
@@ -16949,7 +16963,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="705" spans="1:7" hidden="1">
+    <row r="705" spans="1:7">
       <c r="A705" s="3" t="s">
         <v>87</v>
       </c>
@@ -16972,7 +16986,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="706" spans="1:7" hidden="1">
+    <row r="706" spans="1:7">
       <c r="A706" s="3" t="s">
         <v>87</v>
       </c>
@@ -16995,7 +17009,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="707" spans="1:7" hidden="1">
+    <row r="707" spans="1:7">
       <c r="A707" s="3" t="s">
         <v>87</v>
       </c>
@@ -17018,7 +17032,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="708" spans="1:7" hidden="1">
+    <row r="708" spans="1:7">
       <c r="A708" s="3" t="s">
         <v>87</v>
       </c>
@@ -17041,7 +17055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="709" spans="1:7" hidden="1">
+    <row r="709" spans="1:7">
       <c r="A709" s="3" t="s">
         <v>87</v>
       </c>
@@ -17064,7 +17078,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="710" spans="1:7" hidden="1">
+    <row r="710" spans="1:7">
       <c r="A710" s="3" t="s">
         <v>87</v>
       </c>
@@ -17087,7 +17101,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="711" spans="1:7" hidden="1">
+    <row r="711" spans="1:7">
       <c r="A711" s="3" t="s">
         <v>87</v>
       </c>
@@ -17110,7 +17124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="712" spans="1:7" hidden="1">
+    <row r="712" spans="1:7">
       <c r="A712" s="3" t="s">
         <v>87</v>
       </c>
@@ -17133,7 +17147,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="713" spans="1:7" hidden="1">
+    <row r="713" spans="1:7">
       <c r="A713" s="3" t="s">
         <v>87</v>
       </c>
@@ -17156,7 +17170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="714" spans="1:7" hidden="1">
+    <row r="714" spans="1:7">
       <c r="A714" s="3" t="s">
         <v>87</v>
       </c>
@@ -17179,7 +17193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="715" spans="1:7" hidden="1">
+    <row r="715" spans="1:7">
       <c r="A715" s="3" t="s">
         <v>87</v>
       </c>
@@ -17202,7 +17216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="716" spans="1:7" hidden="1">
+    <row r="716" spans="1:7">
       <c r="A716" s="3" t="s">
         <v>87</v>
       </c>
@@ -17225,7 +17239,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="717" spans="1:7" hidden="1">
+    <row r="717" spans="1:7">
       <c r="A717" s="3" t="s">
         <v>87</v>
       </c>
@@ -17248,7 +17262,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="718" spans="1:7" hidden="1">
+    <row r="718" spans="1:7">
       <c r="A718" s="3" t="s">
         <v>87</v>
       </c>
@@ -17271,7 +17285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="719" spans="1:7" hidden="1">
+    <row r="719" spans="1:7">
       <c r="A719" s="3" t="s">
         <v>87</v>
       </c>
@@ -17294,7 +17308,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="720" spans="1:7" hidden="1">
+    <row r="720" spans="1:7">
       <c r="A720" s="3" t="s">
         <v>87</v>
       </c>
@@ -17317,7 +17331,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="721" spans="1:7" hidden="1">
+    <row r="721" spans="1:7">
       <c r="A721" s="3" t="s">
         <v>87</v>
       </c>
@@ -17340,7 +17354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="722" spans="1:7" hidden="1">
+    <row r="722" spans="1:7">
       <c r="A722" s="3" t="s">
         <v>87</v>
       </c>
@@ -17363,7 +17377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="723" spans="1:7" hidden="1">
+    <row r="723" spans="1:7">
       <c r="A723" s="3" t="s">
         <v>87</v>
       </c>
@@ -17386,7 +17400,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="724" spans="1:7" hidden="1">
+    <row r="724" spans="1:7">
       <c r="A724" s="6" t="s">
         <v>87</v>
       </c>
@@ -17409,7 +17423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="725" spans="1:7" hidden="1">
+    <row r="725" spans="1:7">
       <c r="A725" s="3" t="s">
         <v>87</v>
       </c>
@@ -17432,7 +17446,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="726" spans="1:7" hidden="1">
+    <row r="726" spans="1:7">
       <c r="A726" s="3" t="s">
         <v>87</v>
       </c>
@@ -17455,7 +17469,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="727" spans="1:7" hidden="1">
+    <row r="727" spans="1:7">
       <c r="A727" s="3" t="s">
         <v>87</v>
       </c>
@@ -17478,7 +17492,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="728" spans="1:7" hidden="1">
+    <row r="728" spans="1:7">
       <c r="A728" s="3" t="s">
         <v>87</v>
       </c>
@@ -17501,7 +17515,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="729" spans="1:7" hidden="1">
+    <row r="729" spans="1:7">
       <c r="A729" s="3" t="s">
         <v>87</v>
       </c>
@@ -17524,7 +17538,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="730" spans="1:7" hidden="1">
+    <row r="730" spans="1:7">
       <c r="A730" s="3" t="s">
         <v>87</v>
       </c>
@@ -17547,7 +17561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="731" spans="1:7" hidden="1">
+    <row r="731" spans="1:7">
       <c r="A731" s="3" t="s">
         <v>87</v>
       </c>
@@ -17570,7 +17584,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="732" spans="1:7" hidden="1">
+    <row r="732" spans="1:7">
       <c r="A732" s="3" t="s">
         <v>87</v>
       </c>
@@ -17593,7 +17607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="733" spans="1:7" hidden="1">
+    <row r="733" spans="1:7">
       <c r="A733" s="3" t="s">
         <v>87</v>
       </c>
@@ -17616,7 +17630,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="734" spans="1:7" hidden="1">
+    <row r="734" spans="1:7">
       <c r="A734" s="3" t="s">
         <v>87</v>
       </c>
@@ -17639,7 +17653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="735" spans="1:7" hidden="1">
+    <row r="735" spans="1:7">
       <c r="A735" s="3" t="s">
         <v>87</v>
       </c>
@@ -17662,7 +17676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="736" spans="1:7" hidden="1">
+    <row r="736" spans="1:7">
       <c r="A736" s="3" t="s">
         <v>87</v>
       </c>
@@ -17685,7 +17699,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="737" spans="1:7" hidden="1">
+    <row r="737" spans="1:7">
       <c r="A737" s="3" t="s">
         <v>87</v>
       </c>
@@ -17708,7 +17722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="738" spans="1:7" hidden="1">
+    <row r="738" spans="1:7">
       <c r="A738" s="3" t="s">
         <v>87</v>
       </c>
@@ -17731,7 +17745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="739" spans="1:7" hidden="1">
+    <row r="739" spans="1:7">
       <c r="A739" s="3" t="s">
         <v>87</v>
       </c>
@@ -17754,7 +17768,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="740" spans="1:7" hidden="1">
+    <row r="740" spans="1:7">
       <c r="A740" s="3" t="s">
         <v>87</v>
       </c>
@@ -17777,7 +17791,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="741" spans="1:7" hidden="1">
+    <row r="741" spans="1:7">
       <c r="A741" s="3" t="s">
         <v>87</v>
       </c>
@@ -17800,7 +17814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="742" spans="1:7" hidden="1">
+    <row r="742" spans="1:7">
       <c r="A742" s="3" t="s">
         <v>87</v>
       </c>
@@ -17823,7 +17837,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="743" spans="1:7" hidden="1">
+    <row r="743" spans="1:7">
       <c r="A743" s="3" t="s">
         <v>87</v>
       </c>
@@ -17846,7 +17860,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="744" spans="1:7" hidden="1">
+    <row r="744" spans="1:7">
       <c r="A744" s="3" t="s">
         <v>87</v>
       </c>
@@ -17869,7 +17883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="745" spans="1:7" hidden="1">
+    <row r="745" spans="1:7">
       <c r="A745" s="3" t="s">
         <v>87</v>
       </c>
@@ -17892,7 +17906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="746" spans="1:7" hidden="1">
+    <row r="746" spans="1:7">
       <c r="A746" s="3" t="s">
         <v>87</v>
       </c>
@@ -17915,7 +17929,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="747" spans="1:7" hidden="1">
+    <row r="747" spans="1:7">
       <c r="A747" s="3" t="s">
         <v>87</v>
       </c>
@@ -17938,7 +17952,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="748" spans="1:7" hidden="1">
+    <row r="748" spans="1:7">
       <c r="A748" s="3" t="s">
         <v>87</v>
       </c>
@@ -17961,7 +17975,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="749" spans="1:7" hidden="1">
+    <row r="749" spans="1:7">
       <c r="A749" s="3" t="s">
         <v>87</v>
       </c>
@@ -17984,7 +17998,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="750" spans="1:7" hidden="1">
+    <row r="750" spans="1:7">
       <c r="A750" s="3" t="s">
         <v>87</v>
       </c>
@@ -18007,7 +18021,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="751" spans="1:7" hidden="1">
+    <row r="751" spans="1:7">
       <c r="A751" s="3" t="s">
         <v>87</v>
       </c>
@@ -18030,7 +18044,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="752" spans="1:7" hidden="1">
+    <row r="752" spans="1:7">
       <c r="A752" s="3" t="s">
         <v>87</v>
       </c>
@@ -18053,7 +18067,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="753" spans="1:7" hidden="1">
+    <row r="753" spans="1:7">
       <c r="A753" s="3" t="s">
         <v>87</v>
       </c>
@@ -18076,7 +18090,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="754" spans="1:7" hidden="1">
+    <row r="754" spans="1:7">
       <c r="A754" s="3" t="s">
         <v>87</v>
       </c>
@@ -18099,7 +18113,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="755" spans="1:7" hidden="1">
+    <row r="755" spans="1:7">
       <c r="A755" s="3" t="s">
         <v>87</v>
       </c>
@@ -18122,7 +18136,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="756" spans="1:7" hidden="1">
+    <row r="756" spans="1:7">
       <c r="A756" s="3" t="s">
         <v>87</v>
       </c>
@@ -18145,7 +18159,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="757" spans="1:7" hidden="1">
+    <row r="757" spans="1:7">
       <c r="A757" s="6" t="s">
         <v>97</v>
       </c>
@@ -18168,7 +18182,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="758" spans="1:7" hidden="1">
+    <row r="758" spans="1:7">
       <c r="A758" s="3" t="s">
         <v>97</v>
       </c>
@@ -18191,7 +18205,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="759" spans="1:7" hidden="1">
+    <row r="759" spans="1:7">
       <c r="A759" s="3" t="s">
         <v>97</v>
       </c>
@@ -18214,7 +18228,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="760" spans="1:7" hidden="1">
+    <row r="760" spans="1:7">
       <c r="A760" s="3" t="s">
         <v>97</v>
       </c>
@@ -18237,7 +18251,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="761" spans="1:7" hidden="1">
+    <row r="761" spans="1:7">
       <c r="A761" s="3" t="s">
         <v>97</v>
       </c>
@@ -18260,7 +18274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="762" spans="1:7" hidden="1">
+    <row r="762" spans="1:7">
       <c r="A762" s="3" t="s">
         <v>97</v>
       </c>
@@ -18283,7 +18297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="763" spans="1:7" hidden="1">
+    <row r="763" spans="1:7">
       <c r="A763" s="3" t="s">
         <v>97</v>
       </c>
@@ -18306,7 +18320,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="764" spans="1:7" hidden="1">
+    <row r="764" spans="1:7">
       <c r="A764" s="3" t="s">
         <v>97</v>
       </c>
@@ -18329,7 +18343,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="765" spans="1:7" hidden="1">
+    <row r="765" spans="1:7">
       <c r="A765" s="3" t="s">
         <v>97</v>
       </c>
@@ -18352,7 +18366,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="766" spans="1:7" hidden="1">
+    <row r="766" spans="1:7">
       <c r="A766" s="3" t="s">
         <v>97</v>
       </c>
@@ -18375,7 +18389,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="767" spans="1:7" hidden="1">
+    <row r="767" spans="1:7">
       <c r="A767" s="3" t="s">
         <v>97</v>
       </c>
@@ -18398,7 +18412,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="768" spans="1:7" hidden="1">
+    <row r="768" spans="1:7">
       <c r="A768" s="3" t="s">
         <v>97</v>
       </c>
@@ -18421,7 +18435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="769" spans="1:7" hidden="1">
+    <row r="769" spans="1:7">
       <c r="A769" s="3" t="s">
         <v>97</v>
       </c>
@@ -18444,7 +18458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="770" spans="1:7" hidden="1">
+    <row r="770" spans="1:7">
       <c r="A770" s="3" t="s">
         <v>97</v>
       </c>
@@ -18467,7 +18481,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="771" spans="1:7" hidden="1">
+    <row r="771" spans="1:7">
       <c r="A771" s="3" t="s">
         <v>97</v>
       </c>
@@ -18490,7 +18504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="772" spans="1:7" hidden="1">
+    <row r="772" spans="1:7">
       <c r="A772" s="3" t="s">
         <v>97</v>
       </c>
@@ -18513,7 +18527,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="773" spans="1:7" hidden="1">
+    <row r="773" spans="1:7">
       <c r="A773" s="3" t="s">
         <v>97</v>
       </c>
@@ -18536,7 +18550,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="774" spans="1:7" hidden="1">
+    <row r="774" spans="1:7">
       <c r="A774" s="3" t="s">
         <v>97</v>
       </c>
@@ -18559,7 +18573,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="775" spans="1:7" hidden="1">
+    <row r="775" spans="1:7">
       <c r="A775" s="3" t="s">
         <v>97</v>
       </c>
@@ -18582,7 +18596,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="776" spans="1:7" hidden="1">
+    <row r="776" spans="1:7">
       <c r="A776" s="3" t="s">
         <v>97</v>
       </c>
@@ -18605,7 +18619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="777" spans="1:7" hidden="1">
+    <row r="777" spans="1:7">
       <c r="A777" s="3" t="s">
         <v>97</v>
       </c>
@@ -18628,7 +18642,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="778" spans="1:7" hidden="1">
+    <row r="778" spans="1:7">
       <c r="A778" s="3" t="s">
         <v>97</v>
       </c>
@@ -18651,7 +18665,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="779" spans="1:7" hidden="1">
+    <row r="779" spans="1:7">
       <c r="A779" s="3" t="s">
         <v>97</v>
       </c>
@@ -18674,7 +18688,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="780" spans="1:7" hidden="1">
+    <row r="780" spans="1:7">
       <c r="A780" s="3" t="s">
         <v>97</v>
       </c>
@@ -18697,7 +18711,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="781" spans="1:7" hidden="1">
+    <row r="781" spans="1:7">
       <c r="A781" s="3" t="s">
         <v>97</v>
       </c>
@@ -18720,7 +18734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="782" spans="1:7" hidden="1">
+    <row r="782" spans="1:7">
       <c r="A782" s="3" t="s">
         <v>97</v>
       </c>
@@ -18743,7 +18757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="783" spans="1:7" hidden="1">
+    <row r="783" spans="1:7">
       <c r="A783" s="3" t="s">
         <v>97</v>
       </c>
@@ -18766,7 +18780,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="784" spans="1:7" hidden="1">
+    <row r="784" spans="1:7">
       <c r="A784" s="3" t="s">
         <v>97</v>
       </c>
@@ -18789,7 +18803,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="785" spans="1:7" hidden="1">
+    <row r="785" spans="1:7">
       <c r="A785" s="3" t="s">
         <v>97</v>
       </c>
@@ -18812,7 +18826,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="786" spans="1:7" hidden="1">
+    <row r="786" spans="1:7">
       <c r="A786" s="3" t="s">
         <v>97</v>
       </c>
@@ -18835,7 +18849,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="787" spans="1:7" hidden="1">
+    <row r="787" spans="1:7">
       <c r="A787" s="3" t="s">
         <v>97</v>
       </c>
@@ -18858,7 +18872,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="788" spans="1:7" hidden="1">
+    <row r="788" spans="1:7">
       <c r="A788" s="3" t="s">
         <v>97</v>
       </c>
@@ -18904,7 +18918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="790" spans="1:7" hidden="1">
+    <row r="790" spans="1:7">
       <c r="A790" s="3" t="s">
         <v>97</v>
       </c>
@@ -18927,7 +18941,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="791" spans="1:7" hidden="1">
+    <row r="791" spans="1:7">
       <c r="A791" s="3" t="s">
         <v>97</v>
       </c>
@@ -18950,7 +18964,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="792" spans="1:7" hidden="1">
+    <row r="792" spans="1:7">
       <c r="A792" s="3" t="s">
         <v>97</v>
       </c>
@@ -18973,7 +18987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="793" spans="1:7" hidden="1">
+    <row r="793" spans="1:7">
       <c r="A793" s="3" t="s">
         <v>97</v>
       </c>
@@ -18996,7 +19010,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="794" spans="1:7" hidden="1">
+    <row r="794" spans="1:7">
       <c r="A794" s="3" t="s">
         <v>97</v>
       </c>
@@ -19019,7 +19033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="795" spans="1:7" hidden="1">
+    <row r="795" spans="1:7">
       <c r="A795" s="6" t="s">
         <v>97</v>
       </c>
@@ -19042,7 +19056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="796" spans="1:7" hidden="1">
+    <row r="796" spans="1:7">
       <c r="A796" s="3" t="s">
         <v>97</v>
       </c>
@@ -19065,7 +19079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="797" spans="1:7" hidden="1">
+    <row r="797" spans="1:7">
       <c r="A797" s="3" t="s">
         <v>97</v>
       </c>
@@ -19088,7 +19102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="798" spans="1:7" hidden="1">
+    <row r="798" spans="1:7">
       <c r="A798" s="3" t="s">
         <v>97</v>
       </c>
@@ -19111,7 +19125,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="799" spans="1:7" hidden="1">
+    <row r="799" spans="1:7">
       <c r="A799" s="3" t="s">
         <v>97</v>
       </c>
@@ -19134,7 +19148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="800" spans="1:7" hidden="1">
+    <row r="800" spans="1:7">
       <c r="A800" s="3" t="s">
         <v>97</v>
       </c>
@@ -19157,7 +19171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="801" spans="1:7" hidden="1">
+    <row r="801" spans="1:7">
       <c r="A801" s="3" t="s">
         <v>97</v>
       </c>
@@ -19180,7 +19194,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="802" spans="1:7" hidden="1">
+    <row r="802" spans="1:7">
       <c r="A802" s="3" t="s">
         <v>97</v>
       </c>
@@ -19203,7 +19217,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="803" spans="1:7" hidden="1">
+    <row r="803" spans="1:7">
       <c r="A803" s="3" t="s">
         <v>97</v>
       </c>
@@ -19226,7 +19240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="804" spans="1:7" hidden="1">
+    <row r="804" spans="1:7">
       <c r="A804" s="3" t="s">
         <v>97</v>
       </c>
@@ -19249,7 +19263,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="805" spans="1:7" hidden="1">
+    <row r="805" spans="1:7">
       <c r="A805" s="3" t="s">
         <v>97</v>
       </c>
@@ -19272,7 +19286,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="806" spans="1:7" hidden="1">
+    <row r="806" spans="1:7">
       <c r="A806" s="3" t="s">
         <v>97</v>
       </c>
@@ -19295,7 +19309,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="807" spans="1:7" hidden="1">
+    <row r="807" spans="1:7">
       <c r="A807" s="3" t="s">
         <v>97</v>
       </c>
@@ -19318,7 +19332,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="808" spans="1:7" hidden="1">
+    <row r="808" spans="1:7">
       <c r="A808" s="3" t="s">
         <v>97</v>
       </c>
@@ -19341,7 +19355,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="809" spans="1:7" hidden="1">
+    <row r="809" spans="1:7">
       <c r="A809" s="3" t="s">
         <v>97</v>
       </c>
@@ -19364,7 +19378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="810" spans="1:7" hidden="1">
+    <row r="810" spans="1:7">
       <c r="A810" s="3" t="s">
         <v>97</v>
       </c>
@@ -19387,7 +19401,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="811" spans="1:7" hidden="1">
+    <row r="811" spans="1:7">
       <c r="A811" s="3" t="s">
         <v>97</v>
       </c>
@@ -19410,7 +19424,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="812" spans="1:7" hidden="1">
+    <row r="812" spans="1:7">
       <c r="A812" s="3" t="s">
         <v>97</v>
       </c>
@@ -19433,7 +19447,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="813" spans="1:7" hidden="1">
+    <row r="813" spans="1:7">
       <c r="A813" s="3" t="s">
         <v>97</v>
       </c>
@@ -19456,7 +19470,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="814" spans="1:7" hidden="1">
+    <row r="814" spans="1:7">
       <c r="A814" s="3" t="s">
         <v>97</v>
       </c>
@@ -19479,7 +19493,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="815" spans="1:7" hidden="1">
+    <row r="815" spans="1:7">
       <c r="A815" s="3" t="s">
         <v>97</v>
       </c>
@@ -19502,7 +19516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="816" spans="1:7" hidden="1">
+    <row r="816" spans="1:7">
       <c r="A816" s="3" t="s">
         <v>97</v>
       </c>
@@ -19525,7 +19539,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="817" spans="1:7" hidden="1">
+    <row r="817" spans="1:7">
       <c r="A817" s="3" t="s">
         <v>97</v>
       </c>
@@ -19548,7 +19562,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="818" spans="1:7" hidden="1">
+    <row r="818" spans="1:7">
       <c r="A818" s="3" t="s">
         <v>97</v>
       </c>
@@ -19571,7 +19585,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="819" spans="1:7" hidden="1">
+    <row r="819" spans="1:7">
       <c r="A819" s="3" t="s">
         <v>97</v>
       </c>
@@ -19594,7 +19608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="820" spans="1:7" hidden="1">
+    <row r="820" spans="1:7">
       <c r="A820" s="3" t="s">
         <v>97</v>
       </c>
@@ -19617,7 +19631,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="821" spans="1:7" hidden="1">
+    <row r="821" spans="1:7">
       <c r="A821" s="3" t="s">
         <v>97</v>
       </c>
@@ -19640,7 +19654,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="822" spans="1:7" hidden="1">
+    <row r="822" spans="1:7">
       <c r="A822" s="3" t="s">
         <v>97</v>
       </c>
@@ -19663,7 +19677,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="823" spans="1:7" hidden="1">
+    <row r="823" spans="1:7">
       <c r="A823" s="3" t="s">
         <v>97</v>
       </c>
@@ -19686,7 +19700,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="824" spans="1:7" hidden="1">
+    <row r="824" spans="1:7">
       <c r="A824" s="3" t="s">
         <v>97</v>
       </c>
@@ -19709,7 +19723,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="825" spans="1:7" hidden="1">
+    <row r="825" spans="1:7">
       <c r="A825" s="3" t="s">
         <v>97</v>
       </c>
@@ -19732,7 +19746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="826" spans="1:7" hidden="1">
+    <row r="826" spans="1:7">
       <c r="A826" s="3" t="s">
         <v>97</v>
       </c>
@@ -19755,7 +19769,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="827" spans="1:7" hidden="1">
+    <row r="827" spans="1:7">
       <c r="A827" s="3" t="s">
         <v>97</v>
       </c>
@@ -19778,7 +19792,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="828" spans="1:7" hidden="1">
+    <row r="828" spans="1:7">
       <c r="A828" s="3" t="s">
         <v>97</v>
       </c>
@@ -19801,7 +19815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="829" spans="1:7" hidden="1">
+    <row r="829" spans="1:7">
       <c r="A829" s="3" t="s">
         <v>97</v>
       </c>
@@ -19824,7 +19838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="830" spans="1:7" hidden="1">
+    <row r="830" spans="1:7">
       <c r="A830" s="3" t="s">
         <v>97</v>
       </c>
@@ -19847,7 +19861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="831" spans="1:7" hidden="1">
+    <row r="831" spans="1:7">
       <c r="A831" s="3" t="s">
         <v>97</v>
       </c>
@@ -19870,7 +19884,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="832" spans="1:7" hidden="1">
+    <row r="832" spans="1:7">
       <c r="A832" s="3" t="s">
         <v>97</v>
       </c>
@@ -19893,7 +19907,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="833" spans="1:7" hidden="1">
+    <row r="833" spans="1:7">
       <c r="A833" s="6" t="s">
         <v>97</v>
       </c>
@@ -19916,7 +19930,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="834" spans="1:7" hidden="1">
+    <row r="834" spans="1:7">
       <c r="A834" s="3" t="s">
         <v>97</v>
       </c>
@@ -19939,7 +19953,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="835" spans="1:7" hidden="1">
+    <row r="835" spans="1:7">
       <c r="A835" s="3" t="s">
         <v>97</v>
       </c>
@@ -19962,7 +19976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="836" spans="1:7" hidden="1">
+    <row r="836" spans="1:7">
       <c r="A836" s="3" t="s">
         <v>97</v>
       </c>
@@ -19985,7 +19999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="837" spans="1:7" hidden="1">
+    <row r="837" spans="1:7">
       <c r="A837" s="3" t="s">
         <v>97</v>
       </c>
@@ -20008,7 +20022,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="838" spans="1:7" hidden="1">
+    <row r="838" spans="1:7">
       <c r="A838" s="3" t="s">
         <v>97</v>
       </c>
@@ -20031,7 +20045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="839" spans="1:7" hidden="1">
+    <row r="839" spans="1:7">
       <c r="A839" s="3" t="s">
         <v>97</v>
       </c>
@@ -20054,7 +20068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="840" spans="1:7" hidden="1">
+    <row r="840" spans="1:7">
       <c r="A840" s="3" t="s">
         <v>97</v>
       </c>
@@ -20077,7 +20091,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="841" spans="1:7" hidden="1">
+    <row r="841" spans="1:7">
       <c r="A841" s="3" t="s">
         <v>97</v>
       </c>
@@ -20100,7 +20114,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="842" spans="1:7" hidden="1">
+    <row r="842" spans="1:7">
       <c r="A842" s="3" t="s">
         <v>97</v>
       </c>
@@ -20123,7 +20137,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="843" spans="1:7" hidden="1">
+    <row r="843" spans="1:7">
       <c r="A843" s="3" t="s">
         <v>97</v>
       </c>
@@ -20146,7 +20160,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="844" spans="1:7" hidden="1">
+    <row r="844" spans="1:7">
       <c r="A844" s="3" t="s">
         <v>97</v>
       </c>
@@ -20169,7 +20183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="845" spans="1:7" hidden="1">
+    <row r="845" spans="1:7">
       <c r="A845" s="3" t="s">
         <v>97</v>
       </c>
@@ -20192,7 +20206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="846" spans="1:7" hidden="1">
+    <row r="846" spans="1:7">
       <c r="A846" s="3" t="s">
         <v>97</v>
       </c>
@@ -20215,7 +20229,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="847" spans="1:7" hidden="1">
+    <row r="847" spans="1:7">
       <c r="A847" s="3" t="s">
         <v>97</v>
       </c>
@@ -20238,7 +20252,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="848" spans="1:7" hidden="1">
+    <row r="848" spans="1:7">
       <c r="A848" s="3" t="s">
         <v>97</v>
       </c>
@@ -20261,7 +20275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="849" spans="1:7" hidden="1">
+    <row r="849" spans="1:7">
       <c r="A849" s="3" t="s">
         <v>97</v>
       </c>
@@ -20284,7 +20298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="850" spans="1:7" hidden="1">
+    <row r="850" spans="1:7">
       <c r="A850" s="3" t="s">
         <v>97</v>
       </c>
@@ -20307,7 +20321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="851" spans="1:7" hidden="1">
+    <row r="851" spans="1:7">
       <c r="A851" s="3" t="s">
         <v>97</v>
       </c>
@@ -20330,7 +20344,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="852" spans="1:7" hidden="1">
+    <row r="852" spans="1:7">
       <c r="A852" s="3" t="s">
         <v>97</v>
       </c>
@@ -20353,7 +20367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="853" spans="1:7" hidden="1">
+    <row r="853" spans="1:7">
       <c r="A853" s="3" t="s">
         <v>97</v>
       </c>
@@ -20376,7 +20390,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="854" spans="1:7" hidden="1">
+    <row r="854" spans="1:7">
       <c r="A854" s="3" t="s">
         <v>97</v>
       </c>
@@ -20399,7 +20413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="855" spans="1:7" hidden="1">
+    <row r="855" spans="1:7">
       <c r="A855" s="3" t="s">
         <v>97</v>
       </c>
@@ -20422,7 +20436,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="856" spans="1:7" hidden="1">
+    <row r="856" spans="1:7">
       <c r="A856" s="3" t="s">
         <v>97</v>
       </c>
@@ -20445,7 +20459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="857" spans="1:7" hidden="1">
+    <row r="857" spans="1:7">
       <c r="A857" s="3" t="s">
         <v>97</v>
       </c>
@@ -20468,7 +20482,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="858" spans="1:7" hidden="1">
+    <row r="858" spans="1:7">
       <c r="A858" s="3" t="s">
         <v>97</v>
       </c>
@@ -20491,7 +20505,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="859" spans="1:7" hidden="1">
+    <row r="859" spans="1:7">
       <c r="A859" s="3" t="s">
         <v>97</v>
       </c>
@@ -20514,7 +20528,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="860" spans="1:7" hidden="1">
+    <row r="860" spans="1:7">
       <c r="A860" s="3" t="s">
         <v>97</v>
       </c>
@@ -20537,7 +20551,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="861" spans="1:7" hidden="1">
+    <row r="861" spans="1:7">
       <c r="A861" s="3" t="s">
         <v>97</v>
       </c>
@@ -20560,7 +20574,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="862" spans="1:7" hidden="1">
+    <row r="862" spans="1:7">
       <c r="A862" s="3" t="s">
         <v>97</v>
       </c>
@@ -20583,7 +20597,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="863" spans="1:7" hidden="1">
+    <row r="863" spans="1:7">
       <c r="A863" s="3" t="s">
         <v>97</v>
       </c>
@@ -20606,7 +20620,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="864" spans="1:7" hidden="1">
+    <row r="864" spans="1:7">
       <c r="A864" s="3" t="s">
         <v>97</v>
       </c>
@@ -20629,7 +20643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="865" spans="1:7" hidden="1">
+    <row r="865" spans="1:7">
       <c r="A865" s="3" t="s">
         <v>97</v>
       </c>
@@ -20652,7 +20666,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="866" spans="1:7" hidden="1">
+    <row r="866" spans="1:7">
       <c r="A866" s="3" t="s">
         <v>97</v>
       </c>
@@ -20675,7 +20689,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="867" spans="1:7" hidden="1">
+    <row r="867" spans="1:7">
       <c r="A867" s="3" t="s">
         <v>97</v>
       </c>
@@ -20698,7 +20712,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="868" spans="1:7" hidden="1">
+    <row r="868" spans="1:7">
       <c r="A868" s="3" t="s">
         <v>97</v>
       </c>
@@ -20721,7 +20735,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="869" spans="1:7" hidden="1">
+    <row r="869" spans="1:7">
       <c r="A869" s="3" t="s">
         <v>97</v>
       </c>
@@ -20744,7 +20758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="870" spans="1:7" hidden="1">
+    <row r="870" spans="1:7">
       <c r="A870" s="3" t="s">
         <v>97</v>
       </c>
@@ -20768,18 +20782,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G870" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Aguilar Pedro"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="QRP"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G870" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Public</oddFooter>
